--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/berylzhou/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dskin\Documents\Projects\propensity_score_matching\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3AD8042-9BCA-4443-A8C2-A0440D3D8E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9815A95A-852D-413C-9D2E-02A640BCDD98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35520" yWindow="860" windowWidth="32000" windowHeight="25920" activeTab="1" xr2:uid="{8D6ADBF5-96F6-B143-86A8-5692DBE5BF1C}"/>
+    <workbookView xWindow="-14505" yWindow="-720" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{8D6ADBF5-96F6-B143-86A8-5692DBE5BF1C}"/>
   </bookViews>
   <sheets>
     <sheet name="single stage" sheetId="1" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="268">
   <si>
     <t>dob</t>
   </si>
@@ -114,12 +103,6 @@
     <t>adjuvant chemotherapy (yes=1)</t>
   </si>
   <si>
-    <t xml:space="preserve">neoadjuvant chemotherapy (yes=1) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALND (yes=1) </t>
-  </si>
-  <si>
     <t>sub-pec</t>
   </si>
   <si>
@@ -166,9 +149,6 @@
   </si>
   <si>
     <t>replacement of implant/TE at same time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NSM </t>
   </si>
   <si>
     <t>SSM</t>
@@ -356,9 +336,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">immunotherapy (keytruda?) </t>
-  </si>
-  <si>
     <t>removal of implant 9/20/21</t>
   </si>
   <si>
@@ -490,9 +467,6 @@
   </si>
   <si>
     <t>rupture of breast</t>
-  </si>
-  <si>
-    <t>ADM/dermal sling (type?)</t>
   </si>
   <si>
     <t>pT3N1(mi)</t>
@@ -767,9 +741,6 @@
     </r>
   </si>
   <si>
-    <t>SPY vs ICG lymphography</t>
-  </si>
-  <si>
     <t>socially</t>
   </si>
   <si>
@@ -793,9 +764,6 @@
     <t>IIA</t>
   </si>
   <si>
-    <t>endocrine therapy</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.0 cm </t>
   </si>
   <si>
@@ -1185,18 +1153,6 @@
     <t>other</t>
   </si>
   <si>
-    <t>NSM (mastectomy type)</t>
-  </si>
-  <si>
-    <t>SSM (mastectomy type)</t>
-  </si>
-  <si>
-    <t>POST  chemotherapy (yes=1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRE  chemotherapy (yes=1) </t>
-  </si>
-  <si>
     <t>pain</t>
   </si>
   <si>
@@ -1222,13 +1178,25 @@
   </si>
   <si>
     <t>dehiscence</t>
+  </si>
+  <si>
+    <t>NSM</t>
+  </si>
+  <si>
+    <t>neoadjuvant chemotherapy (yes=1)</t>
+  </si>
+  <si>
+    <t>immunotherapy (keytruda?)</t>
+  </si>
+  <si>
+    <t>ALND (yes=1)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1378,7 +1346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1396,7 +1364,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1411,10 +1378,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -1425,7 +1390,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1765,57 +1729,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F631DC17-C587-D64E-9C79-5E60928EE50E}">
   <dimension ref="A1:BB51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="4" max="4" width="45.6640625" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="45.625" customWidth="1"/>
+    <col min="5" max="5" width="10.625" customWidth="1"/>
     <col min="6" max="6" width="10" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="10.1640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="9.33203125" customWidth="1"/>
-    <col min="11" max="11" width="8.6640625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.33203125" customWidth="1"/>
-    <col min="13" max="13" width="7.33203125" style="3" customWidth="1"/>
-    <col min="14" max="14" width="7.33203125" customWidth="1"/>
+    <col min="7" max="7" width="12.125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="10.125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="9.375" customWidth="1"/>
+    <col min="11" max="11" width="8.625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.375" customWidth="1"/>
+    <col min="13" max="13" width="7.375" style="3" customWidth="1"/>
+    <col min="14" max="14" width="7.375" customWidth="1"/>
     <col min="15" max="15" width="10" style="3" customWidth="1"/>
-    <col min="16" max="16" width="10.6640625" style="3" customWidth="1"/>
-    <col min="17" max="19" width="10.83203125" style="3"/>
+    <col min="16" max="16" width="10.625" style="3" customWidth="1"/>
+    <col min="17" max="19" width="10.875" style="3"/>
     <col min="20" max="20" width="19.5" customWidth="1"/>
-    <col min="21" max="21" width="21.1640625" style="3" customWidth="1"/>
+    <col min="21" max="21" width="21.125" style="3" customWidth="1"/>
     <col min="22" max="22" width="27.5" style="3" customWidth="1"/>
-    <col min="23" max="23" width="28.83203125" customWidth="1"/>
-    <col min="24" max="24" width="15.83203125" customWidth="1"/>
-    <col min="25" max="25" width="21.83203125" style="3" customWidth="1"/>
+    <col min="23" max="23" width="28.875" customWidth="1"/>
+    <col min="24" max="24" width="15.875" customWidth="1"/>
+    <col min="25" max="25" width="21.875" style="3" customWidth="1"/>
     <col min="26" max="26" width="31" style="3" customWidth="1"/>
-    <col min="27" max="27" width="13.83203125" style="3" customWidth="1"/>
-    <col min="28" max="28" width="10.83203125" style="3"/>
-    <col min="29" max="29" width="24.6640625" style="3" customWidth="1"/>
-    <col min="30" max="30" width="22.33203125" style="3" customWidth="1"/>
-    <col min="31" max="31" width="19.83203125" style="3" customWidth="1"/>
-    <col min="32" max="32" width="16.33203125" style="3" customWidth="1"/>
-    <col min="33" max="33" width="10.83203125" style="3"/>
-    <col min="34" max="34" width="17.6640625" style="3" customWidth="1"/>
-    <col min="35" max="35" width="16.33203125" style="3" customWidth="1"/>
-    <col min="36" max="36" width="10.83203125" style="3"/>
-    <col min="37" max="37" width="16.1640625" style="3" customWidth="1"/>
-    <col min="38" max="38" width="19.83203125" style="3" customWidth="1"/>
-    <col min="39" max="39" width="10.83203125" style="35"/>
-    <col min="41" max="41" width="25.1640625" customWidth="1"/>
+    <col min="27" max="27" width="13.875" style="3" customWidth="1"/>
+    <col min="28" max="28" width="10.875" style="3"/>
+    <col min="29" max="29" width="24.625" style="3" customWidth="1"/>
+    <col min="30" max="30" width="22.375" style="3" customWidth="1"/>
+    <col min="31" max="31" width="19.875" style="3" customWidth="1"/>
+    <col min="32" max="32" width="16.375" style="3" customWidth="1"/>
+    <col min="33" max="33" width="10.875" style="3"/>
+    <col min="34" max="34" width="17.625" style="3" customWidth="1"/>
+    <col min="35" max="35" width="16.375" style="3" customWidth="1"/>
+    <col min="36" max="36" width="10.875" style="3"/>
+    <col min="37" max="37" width="16.125" style="3" customWidth="1"/>
+    <col min="38" max="38" width="19.875" style="3" customWidth="1"/>
+    <col min="39" max="39" width="10.875" style="3"/>
+    <col min="41" max="41" width="25.125" customWidth="1"/>
     <col min="42" max="42" width="15.5" customWidth="1"/>
-    <col min="43" max="43" width="16.1640625" style="38" customWidth="1"/>
-    <col min="44" max="44" width="17.5" style="29" customWidth="1"/>
-    <col min="45" max="45" width="18.33203125" style="29" customWidth="1"/>
-    <col min="46" max="46" width="20.83203125" style="29" customWidth="1"/>
-    <col min="47" max="47" width="19.5" style="29" customWidth="1"/>
-    <col min="48" max="48" width="32.6640625" customWidth="1"/>
-    <col min="49" max="49" width="20.5" style="29" customWidth="1"/>
-    <col min="50" max="50" width="21.6640625" style="17" customWidth="1"/>
-    <col min="51" max="51" width="22.6640625" customWidth="1"/>
-    <col min="52" max="52" width="38.83203125" style="29" customWidth="1"/>
-    <col min="53" max="53" width="10.83203125" style="29"/>
+    <col min="43" max="43" width="16.125" style="35" customWidth="1"/>
+    <col min="44" max="44" width="17.5" style="28" customWidth="1"/>
+    <col min="45" max="45" width="18.375" style="28" customWidth="1"/>
+    <col min="46" max="46" width="20.875" style="28" customWidth="1"/>
+    <col min="47" max="47" width="19.5" style="28" customWidth="1"/>
+    <col min="48" max="48" width="32.625" customWidth="1"/>
+    <col min="49" max="49" width="20.5" style="28" customWidth="1"/>
+    <col min="50" max="50" width="21.625" customWidth="1"/>
+    <col min="51" max="51" width="22.625" customWidth="1"/>
+    <col min="52" max="52" width="38.875" style="28" customWidth="1"/>
+    <col min="53" max="53" width="10.875" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:54" s="11" customFormat="1">
       <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
@@ -1823,7 +1787,7 @@
         <v>18</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>20</v>
@@ -1832,34 +1796,34 @@
         <v>0</v>
       </c>
       <c r="F1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="I1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>40</v>
-      </c>
       <c r="N1" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>6</v>
@@ -1871,70 +1835,70 @@
         <v>23</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="V1" s="9" t="s">
-        <v>263</v>
+        <v>41</v>
       </c>
       <c r="W1" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="X1" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Y1" s="9" t="s">
         <v>265</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>264</v>
+        <v>24</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>91</v>
+        <v>266</v>
       </c>
       <c r="AB1" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AC1" s="15" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AD1" s="15" t="s">
-        <v>122</v>
+        <v>11</v>
       </c>
       <c r="AE1" s="9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AF1" s="9" t="s">
-        <v>26</v>
+        <v>267</v>
       </c>
       <c r="AG1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH1" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI1" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="AH1" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI1" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="AJ1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="AK1" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL1" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="AM1" s="33" t="s">
-        <v>58</v>
+        <v>49</v>
+      </c>
+      <c r="AM1" s="31" t="s">
+        <v>55</v>
       </c>
       <c r="AN1" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AO1" s="9" t="s">
         <v>5</v>
@@ -1942,8 +1906,8 @@
       <c r="AP1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="AQ1" s="36" t="s">
-        <v>33</v>
+      <c r="AQ1" s="33" t="s">
+        <v>31</v>
       </c>
       <c r="AR1" s="9" t="s">
         <v>15</v>
@@ -1955,22 +1919,22 @@
         <v>13</v>
       </c>
       <c r="AU1" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AV1" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AW1" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AX1" s="9" t="s">
         <v>14</v>
       </c>
       <c r="AY1" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AZ1" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BA1" s="9" t="s">
         <v>16</v>
@@ -1979,7 +1943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:54">
       <c r="A2">
         <v>2019</v>
       </c>
@@ -1987,31 +1951,31 @@
         <v>43845</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E2" s="12">
         <v>28835</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="18">
         <f ca="1">YEARFRAC(E2,TODAY())</f>
-        <v>47.213888888888889</v>
-      </c>
-      <c r="G2" s="21">
+        <v>47.222222222222221</v>
+      </c>
+      <c r="G2" s="20">
         <v>20.09</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
-      <c r="K2" s="19">
+      <c r="K2" s="18">
         <v>0</v>
       </c>
       <c r="L2" s="1"/>
@@ -2021,28 +1985,28 @@
       <c r="N2">
         <v>0</v>
       </c>
-      <c r="O2" s="19">
-        <v>0</v>
-      </c>
-      <c r="P2" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="19">
-        <v>0</v>
-      </c>
-      <c r="R2" s="19">
-        <v>0</v>
-      </c>
-      <c r="S2" s="19">
+      <c r="O2" s="18">
+        <v>0</v>
+      </c>
+      <c r="P2" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="18">
+        <v>0</v>
+      </c>
+      <c r="R2" s="18">
+        <v>0</v>
+      </c>
+      <c r="S2" s="18">
         <v>1</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2" s="19">
-        <v>1</v>
-      </c>
-      <c r="V2" s="19">
+        <v>26</v>
+      </c>
+      <c r="U2" s="18">
+        <v>1</v>
+      </c>
+      <c r="V2" s="18">
         <v>0</v>
       </c>
       <c r="W2" s="1">
@@ -2051,119 +2015,119 @@
       <c r="X2" s="1">
         <v>0</v>
       </c>
-      <c r="Y2" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="19">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="19">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="19">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="19">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK2" s="19">
+      <c r="Y2" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="18">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="18">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="18">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK2" s="18">
         <v>2</v>
       </c>
-      <c r="AL2" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM2" s="34" t="s">
-        <v>269</v>
+      <c r="AL2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="32" t="s">
+        <v>258</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AP2" s="1">
         <v>0</v>
       </c>
-      <c r="AQ2" s="39">
+      <c r="AQ2" s="36">
         <v>45754</v>
       </c>
-      <c r="AR2" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS2" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
+      <c r="AR2" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS2" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="AT2" s="27"/>
+      <c r="AU2" s="27"/>
       <c r="AV2" s="1">
         <v>0</v>
       </c>
-      <c r="AW2" s="28">
-        <v>0</v>
-      </c>
-      <c r="AX2" s="32"/>
+      <c r="AW2" s="27">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="1"/>
       <c r="AY2" s="1">
         <v>0</v>
       </c>
-      <c r="AZ2" s="28">
-        <v>0</v>
-      </c>
-      <c r="BA2" s="29">
+      <c r="AZ2" s="27">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="28">
         <v>200</v>
       </c>
       <c r="BB2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:54">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B3" s="2">
         <v>43868</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E3" s="2">
         <v>30389</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="18">
         <f t="shared" ref="F3:F20" ca="1" si="0">YEARFRAC(E3,TODAY())</f>
-        <v>42.955555555555556</v>
+        <v>42.963888888888889</v>
       </c>
       <c r="G3" s="5">
         <v>24.72</v>
       </c>
       <c r="H3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2194,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U3" s="3">
         <v>1</v>
@@ -2227,22 +2191,22 @@
         <v>1</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AJ3" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AK3" s="3">
         <v>2</v>
@@ -2250,44 +2214,44 @@
       <c r="AL3" s="3">
         <v>0</v>
       </c>
-      <c r="AM3" s="35" t="s">
-        <v>115</v>
+      <c r="AM3" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="AN3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AO3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
-      <c r="AQ3" s="37">
+      <c r="AQ3" s="34">
         <v>44581</v>
       </c>
-      <c r="AR3" s="29" t="s">
-        <v>57</v>
+      <c r="AR3" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="AV3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AW3" s="29">
+        <v>110</v>
+      </c>
+      <c r="AW3" s="28">
         <v>0</v>
       </c>
       <c r="AY3">
         <v>0</v>
       </c>
-      <c r="AZ3" s="29">
-        <v>0</v>
-      </c>
-      <c r="BA3" s="29">
+      <c r="AZ3" s="28">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="28">
         <v>440</v>
       </c>
       <c r="BB3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:54">
       <c r="A4">
         <v>2020</v>
       </c>
@@ -2295,26 +2259,26 @@
         <v>44027</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E4" s="2">
         <v>31680</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>39.424999999999997</v>
+        <v>39.43333333333333</v>
       </c>
       <c r="G4" s="5">
         <v>22.87</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>74</v>
+        <v>45</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>71</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2345,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U4" s="3">
         <v>1</v>
@@ -2393,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AK4" s="3">
         <v>2</v>
@@ -2401,56 +2365,56 @@
       <c r="AL4" s="3">
         <v>0</v>
       </c>
-      <c r="AM4" s="35" t="s">
-        <v>178</v>
+      <c r="AM4" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="AN4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AO4" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AP4">
         <v>0</v>
       </c>
-      <c r="AQ4" s="37">
+      <c r="AQ4" s="34">
         <v>44775</v>
       </c>
-      <c r="AR4" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS4" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="AT4" s="29" t="s">
+      <c r="AR4" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS4" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="AU4" s="29" t="s">
-        <v>70</v>
+      <c r="AT4" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="AU4" s="28" t="s">
+        <v>67</v>
       </c>
       <c r="AV4">
         <v>0</v>
       </c>
-      <c r="AW4" s="29">
-        <v>1</v>
-      </c>
-      <c r="AX4" s="17" t="s">
-        <v>117</v>
+      <c r="AW4" s="28">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>113</v>
       </c>
       <c r="AY4">
         <v>1</v>
       </c>
-      <c r="AZ4" s="29">
-        <v>1</v>
-      </c>
-      <c r="BA4" s="29">
+      <c r="AZ4" s="28">
+        <v>1</v>
+      </c>
+      <c r="BA4" s="28">
         <v>300</v>
       </c>
       <c r="BB4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:54">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -2458,26 +2422,26 @@
         <v>44048</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E5" s="2">
         <v>23434</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>62.00277777777778</v>
+        <v>62.011111111111113</v>
       </c>
       <c r="G5" s="5">
         <v>24.57</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -2508,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U5" s="3">
         <v>1</v>
@@ -2556,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="AJ5" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AK5" s="3">
         <v>1</v>
@@ -2564,77 +2528,77 @@
       <c r="AL5" s="3">
         <v>1</v>
       </c>
-      <c r="AM5" s="35" t="s">
-        <v>227</v>
+      <c r="AM5" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="AN5" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="AO5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="AP5">
         <v>0</v>
       </c>
-      <c r="AQ5" s="37">
+      <c r="AQ5" s="34">
         <v>45000</v>
       </c>
-      <c r="AR5" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS5" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="AT5" s="29" t="s">
-        <v>66</v>
+      <c r="AR5" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS5" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="AT5" s="28" t="s">
+        <v>63</v>
       </c>
       <c r="AV5" t="s">
-        <v>124</v>
-      </c>
-      <c r="AW5" s="29">
-        <v>1</v>
-      </c>
-      <c r="AX5" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
+      </c>
+      <c r="AW5" s="28">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>122</v>
       </c>
       <c r="AY5">
         <v>1</v>
       </c>
-      <c r="AZ5" s="29">
-        <v>1</v>
-      </c>
-      <c r="BA5" s="29">
+      <c r="AZ5" s="28">
+        <v>1</v>
+      </c>
+      <c r="BA5" s="28">
         <v>425</v>
       </c>
       <c r="BB5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:54">
       <c r="B6" s="2">
         <v>44127</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E6" s="2">
         <v>24739</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>58.427777777777777</v>
+        <v>58.43611111111111</v>
       </c>
       <c r="G6" s="5">
         <v>17.78</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2653,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="Q6" s="3">
         <v>1</v>
@@ -2665,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U6" s="3">
         <v>1</v>
@@ -2679,19 +2643,19 @@
       <c r="X6">
         <v>0</v>
       </c>
-      <c r="Y6" s="26">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="26">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="26">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="26">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="26">
+      <c r="Y6" s="25">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="25">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="25">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="25">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="25">
         <v>0</v>
       </c>
       <c r="AD6" s="3">
@@ -2704,64 +2668,64 @@
         <v>0</v>
       </c>
       <c r="AG6" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AH6" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AI6" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AJ6" s="26" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="AJ6" s="25" t="s">
+        <v>111</v>
       </c>
       <c r="AK6" s="3">
         <v>2</v>
       </c>
-      <c r="AL6" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="AM6" s="35" t="s">
-        <v>115</v>
+      <c r="AL6" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="AM6" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="AN6" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AO6" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AP6">
         <v>0</v>
       </c>
-      <c r="AQ6" s="37">
+      <c r="AQ6" s="34">
         <v>45950</v>
       </c>
-      <c r="AR6" s="30" t="s">
-        <v>57</v>
+      <c r="AR6" s="29" t="s">
+        <v>54</v>
       </c>
       <c r="AV6">
         <v>0</v>
       </c>
-      <c r="AW6" s="29">
-        <v>1</v>
-      </c>
-      <c r="AX6" s="17" t="s">
-        <v>130</v>
+      <c r="AW6" s="28">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>125</v>
       </c>
       <c r="AY6">
         <v>1</v>
       </c>
-      <c r="AZ6" s="29">
-        <v>1</v>
-      </c>
-      <c r="BA6" s="29">
+      <c r="AZ6" s="28">
+        <v>1</v>
+      </c>
+      <c r="BA6" s="28">
         <v>170</v>
       </c>
       <c r="BB6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:54">
       <c r="A7">
         <v>2020</v>
       </c>
@@ -2769,26 +2733,26 @@
         <v>44153</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E7" s="2">
         <v>32050</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>38.411111111111111</v>
+        <v>38.419444444444444</v>
       </c>
       <c r="G7" s="5">
         <v>21.96</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2819,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U7" s="3">
         <v>1</v>
@@ -2867,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AK7" s="3">
         <v>2</v>
@@ -2875,74 +2839,74 @@
       <c r="AL7" s="3">
         <v>1</v>
       </c>
-      <c r="AM7" s="35" t="s">
-        <v>178</v>
+      <c r="AM7" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="AN7" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="AO7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="AP7">
         <v>0</v>
       </c>
-      <c r="AQ7" s="37">
+      <c r="AQ7" s="34">
         <v>45028</v>
       </c>
-      <c r="AR7" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS7" s="29" t="s">
-        <v>266</v>
+      <c r="AR7" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="AS7" s="28" t="s">
+        <v>255</v>
       </c>
       <c r="AV7">
         <v>0</v>
       </c>
-      <c r="AW7" s="29">
+      <c r="AW7" s="28">
         <v>0</v>
       </c>
       <c r="AY7">
         <v>0</v>
       </c>
-      <c r="AZ7" s="29">
-        <v>0</v>
-      </c>
-      <c r="BA7" s="29">
+      <c r="AZ7" s="28">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="28">
         <v>240</v>
       </c>
       <c r="BB7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:54">
       <c r="A8" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B8" s="2">
         <v>44169</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2">
         <v>30752</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>41.963888888888889</v>
+        <v>41.972222222222221</v>
       </c>
       <c r="G8" s="5">
         <v>21.97</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2973,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U8" s="3">
         <v>1</v>
@@ -3006,73 +2970,73 @@
         <v>1</v>
       </c>
       <c r="AE8" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AG8" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AH8" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AI8" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AJ8" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AK8" s="3">
         <v>2</v>
       </c>
       <c r="AL8" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AM8" s="35" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="AM8" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="AN8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AO8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AP8">
         <v>0</v>
       </c>
-      <c r="AQ8" s="37">
+      <c r="AQ8" s="34">
         <v>45419</v>
       </c>
-      <c r="AR8" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS8" s="29" t="s">
-        <v>66</v>
+      <c r="AR8" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS8" s="28" t="s">
+        <v>63</v>
       </c>
       <c r="AV8" t="s">
-        <v>135</v>
-      </c>
-      <c r="AW8" s="29">
-        <v>1</v>
-      </c>
-      <c r="AX8" s="17" t="s">
-        <v>136</v>
+        <v>130</v>
+      </c>
+      <c r="AW8" s="28">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>131</v>
       </c>
       <c r="AY8">
         <v>0</v>
       </c>
-      <c r="AZ8" s="29">
-        <v>0</v>
-      </c>
-      <c r="BA8" s="29">
+      <c r="AZ8" s="28">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="28">
         <v>385</v>
       </c>
       <c r="BB8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:54">
       <c r="A9">
         <v>2020</v>
       </c>
@@ -3080,26 +3044,26 @@
         <v>44188</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2">
         <v>34748</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>31.027777777777779</v>
+        <v>31.036111111111111</v>
       </c>
       <c r="G9" s="5">
         <v>22.31</v>
       </c>
       <c r="H9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3130,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U9" s="3">
         <v>1</v>
@@ -3178,7 +3142,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AK9" s="3">
         <v>0</v>
@@ -3186,44 +3150,44 @@
       <c r="AL9" s="3">
         <v>0</v>
       </c>
-      <c r="AM9" s="35" t="s">
-        <v>105</v>
+      <c r="AM9" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="AN9" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="AO9" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="AP9">
         <v>0</v>
       </c>
-      <c r="AQ9" s="37">
+      <c r="AQ9" s="34">
         <v>45699</v>
       </c>
-      <c r="AR9" s="29" t="s">
-        <v>57</v>
+      <c r="AR9" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="AV9">
         <v>0</v>
       </c>
-      <c r="AW9" s="29">
+      <c r="AW9" s="28">
         <v>0</v>
       </c>
       <c r="AY9">
         <v>0</v>
       </c>
-      <c r="AZ9" s="29">
-        <v>0</v>
-      </c>
-      <c r="BA9" s="29">
+      <c r="AZ9" s="28">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="28">
         <v>205</v>
       </c>
       <c r="BB9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:54">
       <c r="A10">
         <v>2020</v>
       </c>
@@ -3231,26 +3195,26 @@
         <v>44141</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E10" s="2">
         <v>23602</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>61.541666666666664</v>
+        <v>61.55</v>
       </c>
       <c r="G10" s="5">
         <v>19.91</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3281,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U10" s="3">
         <v>1</v>
@@ -3329,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AK10" s="3">
         <v>2</v>
@@ -3337,47 +3301,47 @@
       <c r="AL10" s="3">
         <v>0</v>
       </c>
-      <c r="AM10" s="35">
+      <c r="AM10" s="3">
         <v>0</v>
       </c>
       <c r="AN10" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AO10" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="AP10">
         <v>0</v>
       </c>
-      <c r="AQ10" s="37">
+      <c r="AQ10" s="34">
         <v>46056</v>
       </c>
-      <c r="AR10" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS10" s="29" t="s">
-        <v>267</v>
+      <c r="AR10" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="AS10" s="28" t="s">
+        <v>256</v>
       </c>
       <c r="AV10" t="s">
-        <v>141</v>
-      </c>
-      <c r="AW10" s="29">
+        <v>136</v>
+      </c>
+      <c r="AW10" s="28">
         <v>0</v>
       </c>
       <c r="AY10">
         <v>0</v>
       </c>
-      <c r="AZ10" s="29">
-        <v>0</v>
-      </c>
-      <c r="BA10" s="29">
+      <c r="AZ10" s="28">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="28">
         <v>330</v>
       </c>
       <c r="BB10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:54">
       <c r="A11">
         <v>2020</v>
       </c>
@@ -3385,26 +3349,26 @@
         <v>44027</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E11" s="2">
         <v>31680</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>39.424999999999997</v>
+        <v>39.43333333333333</v>
       </c>
       <c r="G11" s="5">
         <v>22.87</v>
       </c>
       <c r="H11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>74</v>
+        <v>45</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>71</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3435,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U11" s="3">
         <v>1</v>
@@ -3470,7 +3434,7 @@
       <c r="AE11" s="3">
         <v>1</v>
       </c>
-      <c r="AF11" s="20">
+      <c r="AF11" s="19">
         <v>1</v>
       </c>
       <c r="AG11" s="3">
@@ -3483,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="AJ11" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AK11" s="3">
         <v>2</v>
@@ -3491,56 +3455,56 @@
       <c r="AL11" s="3">
         <v>0</v>
       </c>
-      <c r="AM11" s="35" t="s">
-        <v>178</v>
+      <c r="AM11" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="AN11" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AO11" s="6" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="AP11">
         <v>0</v>
       </c>
-      <c r="AQ11" s="37">
+      <c r="AQ11" s="34">
         <v>44775</v>
       </c>
-      <c r="AR11" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS11" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="AT11" s="29" t="s">
-        <v>266</v>
-      </c>
-      <c r="AU11" s="29" t="s">
-        <v>70</v>
+      <c r="AR11" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS11" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="AT11" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="AU11" s="28" t="s">
+        <v>67</v>
       </c>
       <c r="AV11">
         <v>0</v>
       </c>
-      <c r="AW11" s="29">
-        <v>1</v>
-      </c>
-      <c r="AX11" s="17" t="s">
-        <v>147</v>
+      <c r="AW11" s="28">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>142</v>
       </c>
       <c r="AY11">
         <v>1</v>
       </c>
-      <c r="AZ11" s="29">
-        <v>1</v>
-      </c>
-      <c r="BA11" s="29">
+      <c r="AZ11" s="28">
+        <v>1</v>
+      </c>
+      <c r="BA11" s="28">
         <v>300</v>
       </c>
       <c r="BB11" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:54">
       <c r="A12">
         <v>2020</v>
       </c>
@@ -3548,26 +3512,26 @@
         <v>44204</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E12" s="2">
         <v>19447</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>72.913888888888891</v>
+        <v>72.922222222222217</v>
       </c>
       <c r="G12" s="5">
         <v>19.13</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -3597,7 +3561,7 @@
         <v>1</v>
       </c>
       <c r="T12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U12" s="3">
         <v>1</v>
@@ -3645,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="AJ12" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AK12" s="3">
         <v>1</v>
@@ -3653,44 +3617,44 @@
       <c r="AL12" s="3">
         <v>1</v>
       </c>
-      <c r="AM12" s="35" t="s">
-        <v>242</v>
+      <c r="AM12" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="AN12" s="6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AO12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AP12">
         <v>0</v>
       </c>
-      <c r="AQ12" s="37">
+      <c r="AQ12" s="34">
         <v>45915</v>
       </c>
-      <c r="AR12" s="29" t="s">
-        <v>57</v>
+      <c r="AR12" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="AV12">
         <v>0</v>
       </c>
-      <c r="AW12" s="29">
+      <c r="AW12" s="28">
         <v>0</v>
       </c>
       <c r="AY12">
         <v>0</v>
       </c>
-      <c r="AZ12" s="29">
-        <v>0</v>
-      </c>
-      <c r="BA12" s="29">
+      <c r="AZ12" s="28">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="28">
         <v>250</v>
       </c>
       <c r="BB12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:54">
       <c r="A13">
         <v>2020</v>
       </c>
@@ -3698,26 +3662,26 @@
         <v>44251</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E13" s="2">
         <v>22058</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>65.766666666666666</v>
+        <v>65.775000000000006</v>
       </c>
       <c r="G13" s="5">
         <v>21.48</v>
       </c>
       <c r="H13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3735,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
@@ -3747,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U13" s="3">
         <v>0</v>
@@ -3795,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="AJ13" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AK13" s="3">
         <v>0</v>
@@ -3803,50 +3767,50 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
-      <c r="AM13" s="35" t="s">
-        <v>242</v>
+      <c r="AM13" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="AN13" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AO13" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AP13">
         <v>0</v>
       </c>
-      <c r="AQ13" s="37">
+      <c r="AQ13" s="34">
         <v>45776</v>
       </c>
-      <c r="AR13" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS13" s="31" t="s">
-        <v>153</v>
+      <c r="AR13" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="AS13" s="30" t="s">
+        <v>148</v>
       </c>
       <c r="AV13">
         <v>0</v>
       </c>
-      <c r="AW13" s="29">
-        <v>1</v>
-      </c>
-      <c r="AX13" s="17" t="s">
-        <v>153</v>
+      <c r="AW13" s="28">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>148</v>
       </c>
       <c r="AY13">
         <v>1</v>
       </c>
-      <c r="AZ13" s="29">
-        <v>1</v>
-      </c>
-      <c r="BA13" s="29">
+      <c r="AZ13" s="28">
+        <v>1</v>
+      </c>
+      <c r="BA13" s="28">
         <v>375</v>
       </c>
       <c r="BB13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:54">
       <c r="A14">
         <v>2020</v>
       </c>
@@ -3854,26 +3818,26 @@
         <v>44321</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D14" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E14" s="2">
         <v>24201</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>59.9</v>
+        <v>59.908333333333331</v>
       </c>
       <c r="G14" s="5">
         <v>23.63</v>
       </c>
       <c r="H14" t="s">
-        <v>48</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>261</v>
+        <v>45</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>254</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3881,7 +3845,7 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="20">
+      <c r="M14" s="19">
         <v>1</v>
       </c>
       <c r="N14">
@@ -3903,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U14" s="3">
         <v>1</v>
@@ -3917,10 +3881,10 @@
       <c r="X14">
         <v>0</v>
       </c>
-      <c r="Y14" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="20">
+      <c r="Y14" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="19">
         <v>1</v>
       </c>
       <c r="AA14" s="3">
@@ -3936,22 +3900,22 @@
         <v>1</v>
       </c>
       <c r="AE14" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AG14" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AH14" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AI14" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AJ14" s="26" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="AJ14" s="25" t="s">
+        <v>111</v>
       </c>
       <c r="AK14" s="3">
         <v>2</v>
@@ -3959,47 +3923,47 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
-      <c r="AM14" s="27" t="s">
-        <v>115</v>
+      <c r="AM14" s="26" t="s">
+        <v>111</v>
       </c>
       <c r="AN14" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AO14" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AP14">
         <v>0</v>
       </c>
-      <c r="AQ14" s="37">
+      <c r="AQ14" s="34">
         <v>45433</v>
       </c>
-      <c r="AR14" s="29" t="s">
-        <v>57</v>
+      <c r="AR14" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="AV14">
         <v>0</v>
       </c>
-      <c r="AW14" s="29">
-        <v>1</v>
-      </c>
-      <c r="AX14" s="17" t="s">
-        <v>155</v>
+      <c r="AW14" s="28">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>150</v>
       </c>
       <c r="AY14">
         <v>0</v>
       </c>
-      <c r="AZ14" s="29">
-        <v>0</v>
-      </c>
-      <c r="BA14" s="29">
+      <c r="AZ14" s="28">
+        <v>0</v>
+      </c>
+      <c r="BA14" s="28">
         <v>310</v>
       </c>
       <c r="BB14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:54">
       <c r="A15">
         <v>2021</v>
       </c>
@@ -4007,26 +3971,26 @@
         <v>44335</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E15" s="2">
         <v>30784</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>41.87777777777778</v>
+        <v>41.886111111111113</v>
       </c>
       <c r="G15" s="5">
         <v>23.65</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4056,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U15" s="3">
         <v>1</v>
@@ -4104,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="AJ15" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AK15" s="3">
         <v>2</v>
@@ -4112,53 +4076,53 @@
       <c r="AL15" s="3">
         <v>1</v>
       </c>
-      <c r="AM15" s="27" t="s">
-        <v>159</v>
+      <c r="AM15" s="26" t="s">
+        <v>154</v>
       </c>
       <c r="AN15" s="6" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="AO15" s="6" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AP15">
         <v>0</v>
       </c>
-      <c r="AQ15" s="37">
+      <c r="AQ15" s="34">
         <v>45965</v>
       </c>
-      <c r="AR15" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS15" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="AT15" s="29" t="s">
-        <v>153</v>
+      <c r="AR15" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS15" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="AT15" s="28" t="s">
+        <v>148</v>
       </c>
       <c r="AV15">
         <v>0</v>
       </c>
-      <c r="AW15" s="29">
-        <v>1</v>
-      </c>
-      <c r="AX15" s="17" t="s">
-        <v>160</v>
+      <c r="AW15" s="28">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>155</v>
       </c>
       <c r="AY15">
         <v>1</v>
       </c>
-      <c r="AZ15" s="29">
-        <v>1</v>
-      </c>
-      <c r="BA15" s="29">
+      <c r="AZ15" s="28">
+        <v>1</v>
+      </c>
+      <c r="BA15" s="28">
         <v>450</v>
       </c>
       <c r="BB15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:54">
       <c r="A16">
         <v>2017</v>
       </c>
@@ -4166,26 +4130,26 @@
         <v>22</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D16" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E16" s="2">
         <v>24041</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>60.338888888888889</v>
+        <v>60.347222222222221</v>
       </c>
       <c r="G16" s="5">
         <v>21.3</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4203,7 +4167,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="Q16" s="3">
         <v>1</v>
@@ -4215,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U16" s="3">
         <v>0</v>
@@ -4232,7 +4196,7 @@
       <c r="Y16" s="3">
         <v>1</v>
       </c>
-      <c r="Z16" s="20">
+      <c r="Z16" s="19">
         <v>1</v>
       </c>
       <c r="AA16" s="3">
@@ -4268,50 +4232,50 @@
       <c r="AL16" s="3">
         <v>1</v>
       </c>
-      <c r="AM16" s="35" t="s">
-        <v>178</v>
+      <c r="AM16" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="AN16" s="7" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="AP16">
         <v>0</v>
       </c>
-      <c r="AQ16" s="37">
+      <c r="AQ16" s="34">
         <v>45000</v>
       </c>
-      <c r="AR16" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS16" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="AT16" s="29" t="s">
-        <v>153</v>
+      <c r="AR16" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS16" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="AT16" s="28" t="s">
+        <v>148</v>
       </c>
       <c r="AV16">
         <v>0</v>
       </c>
-      <c r="AW16" s="29">
-        <v>1</v>
-      </c>
-      <c r="AX16" s="17" t="s">
-        <v>163</v>
+      <c r="AW16" s="28">
+        <v>1</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>158</v>
       </c>
       <c r="AY16">
         <v>0</v>
       </c>
-      <c r="AZ16" s="29">
-        <v>0</v>
-      </c>
-      <c r="BA16" s="29">
+      <c r="AZ16" s="28">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="28">
         <v>190</v>
       </c>
       <c r="BB16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:54">
       <c r="A17">
         <v>2021</v>
       </c>
@@ -4319,26 +4283,26 @@
         <v>44512</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D17" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E17" s="2">
         <v>27390</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>51.169444444444444</v>
+        <v>51.177777777777777</v>
       </c>
       <c r="G17" s="5">
         <v>21.7</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4356,7 +4320,7 @@
         <v>1</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="Q17" s="3">
         <v>1</v>
@@ -4368,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U17" s="3">
         <v>1</v>
@@ -4416,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="AJ17" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AK17" s="3">
         <v>1</v>
@@ -4424,44 +4388,44 @@
       <c r="AL17" s="3">
         <v>1</v>
       </c>
-      <c r="AM17" s="27">
+      <c r="AM17" s="26">
         <v>0</v>
       </c>
       <c r="AO17" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AP17">
         <v>0</v>
       </c>
-      <c r="AQ17" s="37">
+      <c r="AQ17" s="34">
         <v>46055</v>
       </c>
-      <c r="AR17" s="29" t="s">
-        <v>57</v>
+      <c r="AR17" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="AV17">
         <v>0</v>
       </c>
-      <c r="AW17" s="29">
-        <v>1</v>
-      </c>
-      <c r="AX17" s="17" t="s">
-        <v>165</v>
+      <c r="AW17" s="28">
+        <v>1</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>160</v>
       </c>
       <c r="AY17">
         <v>1</v>
       </c>
-      <c r="AZ17" s="29">
-        <v>1</v>
-      </c>
-      <c r="BA17" s="29">
+      <c r="AZ17" s="28">
+        <v>1</v>
+      </c>
+      <c r="BA17" s="28">
         <v>405</v>
       </c>
       <c r="BB17" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:54">
       <c r="A18">
         <v>2021</v>
       </c>
@@ -4469,26 +4433,26 @@
         <v>44610</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E18" s="2">
         <v>23082</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>62.961111111111109</v>
+        <v>62.969444444444441</v>
       </c>
       <c r="G18" s="5">
         <v>25.34</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4497,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4506,7 +4470,7 @@
         <v>1</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="Q18" s="3">
         <v>0</v>
@@ -4518,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U18" s="3">
         <v>1</v>
@@ -4566,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="AJ18" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AK18" s="3">
         <v>0</v>
@@ -4574,71 +4538,71 @@
       <c r="AL18" s="3">
         <v>0</v>
       </c>
-      <c r="AM18" s="27" t="s">
-        <v>242</v>
+      <c r="AM18" s="26" t="s">
+        <v>235</v>
       </c>
       <c r="AN18" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AO18" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AP18">
         <v>0</v>
       </c>
-      <c r="AQ18" s="37">
+      <c r="AQ18" s="34">
         <v>45495</v>
       </c>
-      <c r="AR18" s="29" t="s">
-        <v>57</v>
+      <c r="AR18" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="AV18">
         <v>0</v>
       </c>
-      <c r="AW18" s="29">
+      <c r="AW18" s="28">
         <v>0</v>
       </c>
       <c r="AY18">
         <v>0</v>
       </c>
-      <c r="AZ18" s="29">
-        <v>0</v>
-      </c>
-      <c r="BA18" s="29">
+      <c r="AZ18" s="28">
+        <v>0</v>
+      </c>
+      <c r="BA18" s="28">
         <v>485</v>
       </c>
       <c r="BB18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:54">
       <c r="A19" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B19" s="2">
         <v>44617</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D19" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E19" s="2">
         <v>23630</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>61.466666666666669</v>
+        <v>61.475000000000001</v>
       </c>
       <c r="G19" s="5">
         <v>24.41</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4668,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U19" s="3">
         <v>1</v>
@@ -4716,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="AJ19" s="3" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AK19" s="3">
         <v>2</v>
@@ -4724,50 +4688,50 @@
       <c r="AL19" s="3">
         <v>2</v>
       </c>
-      <c r="AM19" s="27" t="s">
-        <v>242</v>
+      <c r="AM19" s="26" t="s">
+        <v>235</v>
       </c>
       <c r="AN19" s="6" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AO19" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AP19">
         <v>0</v>
       </c>
-      <c r="AQ19" s="37">
+      <c r="AQ19" s="34">
         <v>45601</v>
       </c>
-      <c r="AR19" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS19" s="29" t="s">
-        <v>70</v>
+      <c r="AR19" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS19" s="28" t="s">
+        <v>67</v>
       </c>
       <c r="AV19">
         <v>0</v>
       </c>
-      <c r="AW19" s="29">
-        <v>1</v>
-      </c>
-      <c r="AX19" s="17" t="s">
-        <v>236</v>
+      <c r="AW19" s="28">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>229</v>
       </c>
       <c r="AY19">
         <v>1</v>
       </c>
-      <c r="AZ19" s="29">
-        <v>1</v>
-      </c>
-      <c r="BA19" s="29">
+      <c r="AZ19" s="28">
+        <v>1</v>
+      </c>
+      <c r="BA19" s="28">
         <v>405</v>
       </c>
       <c r="BB19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:54">
       <c r="A20">
         <v>2021</v>
       </c>
@@ -4775,26 +4739,26 @@
         <v>44673</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E20" s="2">
         <v>21495</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>67.311111111111117</v>
+        <v>67.319444444444443</v>
       </c>
       <c r="G20" s="5">
         <v>32.81</v>
       </c>
       <c r="H20" t="s">
-        <v>48</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>74</v>
+        <v>45</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>71</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -4824,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="U20" s="3">
         <v>1</v>
@@ -4869,10 +4833,10 @@
         <v>1</v>
       </c>
       <c r="AI20" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AJ20" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="AK20" s="3">
         <v>0</v>
@@ -4880,84 +4844,84 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
-      <c r="AM20" s="35">
+      <c r="AM20" s="3">
         <v>0</v>
       </c>
       <c r="AN20" s="7" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="AO20" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="AP20">
         <v>0</v>
       </c>
-      <c r="AQ20" s="37">
+      <c r="AQ20" s="34">
         <v>45923</v>
       </c>
-      <c r="AR20" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS20" s="29" t="s">
-        <v>126</v>
+      <c r="AR20" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS20" s="28" t="s">
+        <v>121</v>
       </c>
       <c r="AV20" t="s">
-        <v>241</v>
-      </c>
-      <c r="AW20" s="29">
+        <v>234</v>
+      </c>
+      <c r="AW20" s="28">
         <v>0</v>
       </c>
       <c r="AY20">
         <v>0</v>
       </c>
-      <c r="AZ20" s="29">
-        <v>0</v>
-      </c>
-      <c r="BA20" s="29">
+      <c r="AZ20" s="28">
+        <v>0</v>
+      </c>
+      <c r="BA20" s="28">
         <v>445</v>
       </c>
       <c r="BB20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="40" spans="5:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="5:16">
       <c r="E40" s="4"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="22"/>
-      <c r="I40" s="20"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="21"/>
+      <c r="I40" s="19"/>
       <c r="J40" s="4"/>
-      <c r="K40" s="20"/>
+      <c r="K40" s="19"/>
       <c r="L40" s="4"/>
-      <c r="M40" s="20"/>
+      <c r="M40" s="19"/>
       <c r="N40" s="4"/>
-      <c r="O40" s="20"/>
-      <c r="P40" s="20"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
     </row>
-    <row r="41" spans="5:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="5:16">
       <c r="E41" s="4"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="22"/>
-      <c r="I41" s="20"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="21"/>
+      <c r="I41" s="19"/>
       <c r="J41" s="4"/>
-      <c r="K41" s="20"/>
+      <c r="K41" s="19"/>
       <c r="L41" s="4"/>
-      <c r="M41" s="20"/>
+      <c r="M41" s="19"/>
       <c r="N41" s="4"/>
-      <c r="O41" s="20"/>
-      <c r="P41" s="20"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
     </row>
-    <row r="51" spans="5:16" x14ac:dyDescent="0.2">
+    <row r="51" spans="5:16">
       <c r="E51" s="4"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="22"/>
-      <c r="I51" s="20"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="21"/>
+      <c r="I51" s="19"/>
       <c r="J51" s="4"/>
-      <c r="K51" s="20"/>
+      <c r="K51" s="19"/>
       <c r="L51" s="4"/>
-      <c r="M51" s="20"/>
+      <c r="M51" s="19"/>
       <c r="N51" s="4"/>
-      <c r="O51" s="20"/>
-      <c r="P51" s="20"/>
+      <c r="O51" s="19"/>
+      <c r="P51" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4968,56 +4932,56 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{820114AD-64C4-5043-9A40-8597C3FEAC44}">
   <dimension ref="A1:BF30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="3"/>
-    <col min="5" max="5" width="31.6640625" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="22.875" customWidth="1"/>
+    <col min="4" max="4" width="10.875" style="3"/>
+    <col min="5" max="5" width="31.625" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="5" customWidth="1"/>
     <col min="8" max="8" width="10" style="5" customWidth="1"/>
-    <col min="9" max="9" width="12.1640625" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" style="3"/>
-    <col min="11" max="11" width="18.1640625" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="5.1640625" customWidth="1"/>
-    <col min="14" max="15" width="7.33203125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="11.83203125" style="3" customWidth="1"/>
-    <col min="17" max="17" width="13.1640625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="10.83203125" style="3"/>
+    <col min="9" max="9" width="12.125" customWidth="1"/>
+    <col min="10" max="10" width="10.875" style="3"/>
+    <col min="11" max="11" width="18.125" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="5.125" customWidth="1"/>
+    <col min="14" max="15" width="7.375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="13.125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="10.875" style="3"/>
     <col min="19" max="19" width="10" style="3" customWidth="1"/>
-    <col min="20" max="20" width="10.6640625" style="3" customWidth="1"/>
-    <col min="22" max="23" width="10.83203125" style="3"/>
+    <col min="20" max="20" width="10.625" style="3" customWidth="1"/>
+    <col min="22" max="23" width="10.875" style="3"/>
     <col min="24" max="24" width="19.5" customWidth="1"/>
-    <col min="25" max="25" width="21.1640625" customWidth="1"/>
+    <col min="25" max="25" width="21.125" customWidth="1"/>
     <col min="26" max="26" width="27.5" style="3" customWidth="1"/>
-    <col min="27" max="27" width="28.83203125" style="3" customWidth="1"/>
-    <col min="28" max="28" width="15.83203125" style="3" customWidth="1"/>
-    <col min="29" max="30" width="10.83203125" style="3"/>
-    <col min="31" max="31" width="17.33203125" style="3" customWidth="1"/>
-    <col min="32" max="32" width="13.83203125" style="3" customWidth="1"/>
-    <col min="33" max="34" width="10.83203125" style="3"/>
+    <col min="27" max="27" width="28.875" style="3" customWidth="1"/>
+    <col min="28" max="28" width="15.875" style="3" customWidth="1"/>
+    <col min="29" max="30" width="10.875" style="3"/>
+    <col min="31" max="31" width="17.375" style="3" customWidth="1"/>
+    <col min="32" max="32" width="13.875" style="3" customWidth="1"/>
+    <col min="33" max="34" width="10.875" style="3"/>
     <col min="35" max="35" width="10" style="3" customWidth="1"/>
     <col min="36" max="36" width="9" style="3" customWidth="1"/>
-    <col min="37" max="37" width="10.83203125" style="3"/>
-    <col min="38" max="38" width="17.6640625" style="3" customWidth="1"/>
-    <col min="39" max="39" width="20.1640625" style="3" customWidth="1"/>
-    <col min="40" max="40" width="16.33203125" style="3" customWidth="1"/>
-    <col min="41" max="41" width="14.1640625" customWidth="1"/>
-    <col min="44" max="44" width="25.1640625" style="38" customWidth="1"/>
-    <col min="45" max="45" width="15.5" style="38" customWidth="1"/>
-    <col min="46" max="46" width="16.1640625" style="38" customWidth="1"/>
-    <col min="47" max="48" width="17.5" style="38" customWidth="1"/>
+    <col min="37" max="37" width="10.875" style="3"/>
+    <col min="38" max="38" width="17.625" style="3" customWidth="1"/>
+    <col min="39" max="39" width="20.125" style="3" customWidth="1"/>
+    <col min="40" max="40" width="16.375" style="3" customWidth="1"/>
+    <col min="41" max="41" width="14.125" customWidth="1"/>
+    <col min="44" max="44" width="25.125" style="35" customWidth="1"/>
+    <col min="45" max="45" width="15.5" style="35" customWidth="1"/>
+    <col min="46" max="46" width="16.125" style="35" customWidth="1"/>
+    <col min="47" max="48" width="17.5" style="35" customWidth="1"/>
     <col min="49" max="49" width="17.5" customWidth="1"/>
-    <col min="50" max="50" width="18.33203125" style="38" customWidth="1"/>
-    <col min="51" max="51" width="20.83203125" customWidth="1"/>
+    <col min="50" max="50" width="18.375" style="35" customWidth="1"/>
+    <col min="51" max="51" width="20.875" customWidth="1"/>
     <col min="52" max="52" width="19.5" customWidth="1"/>
-    <col min="53" max="53" width="32.6640625" style="38" customWidth="1"/>
-    <col min="54" max="54" width="13" style="38" customWidth="1"/>
-    <col min="55" max="56" width="10.83203125" style="38"/>
+    <col min="53" max="53" width="32.625" style="35" customWidth="1"/>
+    <col min="54" max="54" width="13" style="35" customWidth="1"/>
+    <col min="55" max="56" width="10.875" style="35"/>
     <col min="57" max="57" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:58" s="11" customFormat="1">
       <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
@@ -5027,8 +4991,8 @@
       <c r="C1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="23" t="s">
-        <v>253</v>
+      <c r="D1" s="22" t="s">
+        <v>246</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>20</v>
@@ -5036,110 +5000,110 @@
       <c r="F1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="J1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="L1" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="N1" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N1" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="O1" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="P1" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q1" s="23" t="s">
+      <c r="O1" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="23" t="s">
+      <c r="R1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="23" t="s">
+      <c r="S1" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="23" t="s">
-        <v>27</v>
+      <c r="T1" s="22" t="s">
+        <v>25</v>
       </c>
       <c r="U1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="23" t="s">
+      <c r="V1" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="W1" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="X1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z1" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA1" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB1" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="AC1" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="W1" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="X1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y1" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z1" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB1" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC1" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD1" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="AE1" s="23" t="s">
+      <c r="AD1" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="AF1" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG1" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH1" s="23" t="s">
+      <c r="AF1" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG1" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="AH1" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI1" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ1" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="AI1" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ1" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="AK1" s="23" t="s">
+      <c r="AK1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="AL1" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="AM1" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AN1" s="23" t="s">
-        <v>58</v>
+      <c r="AL1" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM1" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN1" s="22" t="s">
+        <v>55</v>
       </c>
       <c r="AO1" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AP1" s="9" t="s">
         <v>5</v>
@@ -5147,50 +5111,50 @@
       <c r="AQ1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="AR1" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="AS1" s="36" t="s">
+      <c r="AR1" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="AT1" s="36" t="s">
+      <c r="AT1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="AU1" s="36" t="s">
+      <c r="AU1" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="AV1" s="36" t="s">
-        <v>77</v>
+      <c r="AV1" s="33" t="s">
+        <v>74</v>
       </c>
       <c r="AW1" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="AX1" s="36" t="s">
-        <v>55</v>
+        <v>44</v>
+      </c>
+      <c r="AX1" s="33" t="s">
+        <v>52</v>
       </c>
       <c r="AY1" s="9" t="s">
         <v>14</v>
       </c>
       <c r="AZ1" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="BA1" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="BB1" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="BA1" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="BB1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="BC1" s="36" t="s">
+      <c r="BC1" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="BD1" s="36" t="s">
+      <c r="BD1" s="33" t="s">
         <v>16</v>
       </c>
       <c r="BE1" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:58">
       <c r="A2">
         <v>1999</v>
       </c>
@@ -5200,27 +5164,27 @@
       <c r="C2" s="2">
         <v>43900</v>
       </c>
-      <c r="D2" s="24" t="s">
-        <v>64</v>
+      <c r="D2" s="23" t="s">
+        <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F2" s="2">
         <v>24947</v>
       </c>
       <c r="G2" s="5">
         <f ca="1">YEARFRAC(F2,TODAY())</f>
-        <v>57.858333333333334</v>
+        <v>57.866666666666667</v>
       </c>
       <c r="H2" s="5">
         <v>25.01</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -5250,7 +5214,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V2" s="3">
         <v>0</v>
@@ -5298,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AL2" s="3">
         <v>2</v>
@@ -5307,58 +5271,58 @@
         <v>1</v>
       </c>
       <c r="AN2" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="AO2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AP2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="34">
+        <v>44732</v>
+      </c>
+      <c r="AS2" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="AT2" s="35">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="35">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="35">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="s">
         <v>51</v>
       </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2" s="37">
-        <v>44732</v>
-      </c>
-      <c r="AS2" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT2" s="38">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="38">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2" s="38">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>54</v>
-      </c>
       <c r="AZ2">
         <v>0</v>
       </c>
-      <c r="BA2" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB2" s="38">
+      <c r="BA2" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="35">
         <v>350</v>
       </c>
-      <c r="BC2" s="38">
+      <c r="BC2" s="35">
         <v>250</v>
       </c>
-      <c r="BD2" s="38">
+      <c r="BD2" s="35">
         <v>350</v>
       </c>
       <c r="BE2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:58">
       <c r="A3">
         <v>2019</v>
       </c>
@@ -5368,27 +5332,27 @@
       <c r="C3" s="2">
         <v>44042</v>
       </c>
-      <c r="D3" s="24" t="s">
-        <v>64</v>
+      <c r="D3" s="23" t="s">
+        <v>61</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F3" s="2">
         <v>17830</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" ref="G3:G30" ca="1" si="0">YEARFRAC(F3,TODAY())</f>
-        <v>77.344444444444449</v>
+        <v>77.352777777777774</v>
       </c>
       <c r="H3" s="5">
         <v>26.44</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -5418,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V3" s="3">
         <v>0</v>
@@ -5466,67 +5430,67 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL3" s="3">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="3">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="34">
+        <v>44343</v>
+      </c>
+      <c r="AS3" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="AL3" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM3" s="3">
-        <v>1</v>
-      </c>
-      <c r="AN3" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="6" t="s">
+      <c r="AT3" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU3" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW3">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="35">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="s">
         <v>65</v>
       </c>
-      <c r="AP3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="37">
-        <v>44343</v>
-      </c>
-      <c r="AS3" s="38" t="s">
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="35">
+        <v>650</v>
+      </c>
+      <c r="BC3" s="35">
+        <v>100</v>
+      </c>
+      <c r="BD3" s="35">
+        <v>650</v>
+      </c>
+      <c r="BE3" t="s">
         <v>53</v>
       </c>
-      <c r="AT3" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="AU3" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="AW3">
-        <v>1</v>
-      </c>
-      <c r="AX3" s="38">
-        <v>1</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB3" s="38">
-        <v>650</v>
-      </c>
-      <c r="BC3" s="38">
-        <v>100</v>
-      </c>
-      <c r="BD3" s="38">
-        <v>650</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>56</v>
-      </c>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:58">
       <c r="A4">
         <v>2019</v>
       </c>
@@ -5536,27 +5500,27 @@
       <c r="C4" s="2">
         <v>43985</v>
       </c>
-      <c r="D4" s="24" t="s">
-        <v>73</v>
+      <c r="D4" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F4" s="2">
         <v>31030</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>41.205555555555556</v>
+        <v>41.213888888888889</v>
       </c>
       <c r="H4" s="5">
         <v>21.68</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -5586,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V4" s="3">
         <v>1</v>
@@ -5634,64 +5598,64 @@
         <v>1</v>
       </c>
       <c r="AK4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="34">
+        <v>44502</v>
+      </c>
+      <c r="AS4" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="AL4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="AO4" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="37">
-        <v>44502</v>
-      </c>
-      <c r="AS4" s="38" t="s">
+      <c r="AT4" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU4" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW4">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="35">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="35">
+        <v>450</v>
+      </c>
+      <c r="BC4" s="35">
+        <v>150</v>
+      </c>
+      <c r="BD4" s="35">
+        <v>545</v>
+      </c>
+      <c r="BE4" t="s">
         <v>53</v>
       </c>
-      <c r="AT4" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU4" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="AW4">
-        <v>1</v>
-      </c>
-      <c r="AX4" s="38">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB4" s="38">
-        <v>450</v>
-      </c>
-      <c r="BC4" s="38">
-        <v>150</v>
-      </c>
-      <c r="BD4" s="38">
-        <v>545</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>56</v>
-      </c>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:58">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -5701,27 +5665,27 @@
       <c r="C5" s="2">
         <v>44244</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>270</v>
+      <c r="D5" s="23" t="s">
+        <v>259</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F5" s="2">
         <v>26142</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>54.583333333333336</v>
+        <v>54.591666666666669</v>
       </c>
       <c r="H5" s="5">
         <v>18.21</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -5751,7 +5715,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V5" s="3">
         <v>1</v>
@@ -5799,70 +5763,70 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="AO5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="34">
+        <v>45887</v>
+      </c>
+      <c r="AS5" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="AL5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="AO5" s="6" t="s">
+      <c r="AT5" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU5" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="AP5" t="s">
-        <v>72</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="37">
-        <v>45887</v>
-      </c>
-      <c r="AS5" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT5" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU5" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV5" s="38" t="s">
-        <v>217</v>
+      <c r="AV5" s="35" t="s">
+        <v>210</v>
       </c>
       <c r="AW5">
         <v>1</v>
       </c>
-      <c r="AX5" s="38">
+      <c r="AX5" s="35">
         <v>1</v>
       </c>
       <c r="AY5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AZ5">
         <v>1</v>
       </c>
-      <c r="BA5" s="38">
-        <v>1</v>
-      </c>
-      <c r="BB5" s="38">
+      <c r="BA5" s="35">
+        <v>1</v>
+      </c>
+      <c r="BB5" s="35">
         <v>250</v>
       </c>
-      <c r="BC5" s="38">
-        <v>0</v>
-      </c>
-      <c r="BD5" s="38">
+      <c r="BC5" s="35">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="35">
         <v>170</v>
       </c>
       <c r="BE5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:58">
       <c r="A6">
         <v>2014</v>
       </c>
@@ -5872,27 +5836,27 @@
       <c r="C6" s="2">
         <v>44026</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>258</v>
+      <c r="D6" s="23" t="s">
+        <v>251</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F6" s="2">
         <v>29260</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>46.052777777777777</v>
+        <v>46.06111111111111</v>
       </c>
       <c r="H6" s="5">
         <v>25.55</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -5922,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V6" s="3">
         <v>0</v>
@@ -5931,10 +5895,10 @@
         <v>1</v>
       </c>
       <c r="X6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Y6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Z6" s="3">
         <v>1</v>
@@ -5970,7 +5934,7 @@
         <v>1</v>
       </c>
       <c r="AK6" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AL6" s="3">
         <v>2</v>
@@ -5979,49 +5943,49 @@
         <v>1</v>
       </c>
       <c r="AN6" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AO6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AP6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AQ6">
         <v>0</v>
       </c>
-      <c r="AR6" s="37">
+      <c r="AR6" s="34">
         <v>46042</v>
       </c>
-      <c r="AS6" s="38" t="s">
-        <v>57</v>
+      <c r="AS6" s="35" t="s">
+        <v>54</v>
       </c>
       <c r="AW6">
         <v>0</v>
       </c>
-      <c r="AX6" s="38">
+      <c r="AX6" s="35">
         <v>0</v>
       </c>
       <c r="AZ6">
         <v>0</v>
       </c>
-      <c r="BA6" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB6" s="38">
+      <c r="BA6" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="35">
         <v>300</v>
       </c>
-      <c r="BC6" s="38">
+      <c r="BC6" s="35">
         <v>200</v>
       </c>
-      <c r="BD6" s="38">
+      <c r="BD6" s="35">
         <v>300</v>
       </c>
       <c r="BE6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:58">
       <c r="A7">
         <v>2019</v>
       </c>
@@ -6031,27 +5995,27 @@
       <c r="C7" s="2">
         <v>44084</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>93</v>
+      <c r="D7" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="F7" s="2">
         <v>28651</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>47.716666666666669</v>
+        <v>47.725000000000001</v>
       </c>
       <c r="H7" s="5">
         <v>24.34</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -6081,7 +6045,7 @@
         <v>1</v>
       </c>
       <c r="U7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V7" s="3">
         <v>0</v>
@@ -6129,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AL7" s="3">
         <v>2</v>
@@ -6141,49 +6105,49 @@
         <v>0</v>
       </c>
       <c r="AO7" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AP7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AQ7">
         <v>0</v>
       </c>
-      <c r="AR7" s="37">
+      <c r="AR7" s="34">
         <v>45965</v>
       </c>
-      <c r="AS7" s="38" t="s">
-        <v>57</v>
+      <c r="AS7" s="35" t="s">
+        <v>54</v>
       </c>
       <c r="AW7">
         <v>0</v>
       </c>
-      <c r="AX7" s="38">
+      <c r="AX7" s="35">
         <v>1</v>
       </c>
       <c r="AY7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AZ7">
         <v>1</v>
       </c>
-      <c r="BA7" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB7" s="38">
+      <c r="BA7" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="35">
         <v>550</v>
       </c>
-      <c r="BC7" s="38">
+      <c r="BC7" s="35">
         <v>400</v>
       </c>
-      <c r="BD7" s="38" t="s">
-        <v>87</v>
+      <c r="BD7" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="BE7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:58">
       <c r="A8">
         <v>2019</v>
       </c>
@@ -6193,27 +6157,27 @@
       <c r="C8" s="2">
         <v>44089</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>73</v>
+      <c r="D8" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F8" s="2">
         <v>24762</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>58.363888888888887</v>
+        <v>58.37222222222222</v>
       </c>
       <c r="H8" s="5">
         <v>22.1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -6243,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V8" s="3">
         <v>1</v>
@@ -6291,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AL8" s="3">
         <v>2</v>
@@ -6300,52 +6264,52 @@
         <v>1</v>
       </c>
       <c r="AN8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO8" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="34">
+        <v>44217</v>
+      </c>
+      <c r="AS8" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="AT8" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="35">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="35">
+        <v>550</v>
+      </c>
+      <c r="BC8" s="35">
         <v>100</v>
       </c>
-      <c r="AO8" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>95</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8" s="37">
-        <v>44217</v>
-      </c>
-      <c r="AS8" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT8" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8" s="38">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB8" s="38">
-        <v>550</v>
-      </c>
-      <c r="BC8" s="38">
-        <v>100</v>
-      </c>
-      <c r="BD8" s="38">
+      <c r="BD8" s="35">
         <v>525</v>
       </c>
       <c r="BE8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:58">
       <c r="A9">
         <v>2020</v>
       </c>
@@ -6355,27 +6319,27 @@
       <c r="C9" s="2">
         <v>44012</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>73</v>
+      <c r="D9" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F9" s="2">
         <v>24595</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>58.819444444444443</v>
+        <v>58.827777777777776</v>
       </c>
       <c r="H9" s="5">
         <v>23.49</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -6405,7 +6369,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V9" s="3">
         <v>1</v>
@@ -6453,67 +6417,67 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="34">
+        <v>44622</v>
+      </c>
+      <c r="AS9" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="AL9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>101</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>103</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="37">
-        <v>44622</v>
-      </c>
-      <c r="AS9" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT9" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="AU9" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="AV9" s="38" t="s">
-        <v>217</v>
+      <c r="AT9" s="35" t="s">
+        <v>260</v>
+      </c>
+      <c r="AU9" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV9" s="35" t="s">
+        <v>210</v>
       </c>
       <c r="AW9">
         <v>0</v>
       </c>
-      <c r="AX9" s="38">
+      <c r="AX9" s="35">
         <v>0</v>
       </c>
       <c r="AZ9">
         <v>0</v>
       </c>
-      <c r="BA9" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB9" s="38">
+      <c r="BA9" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="35">
         <v>550</v>
       </c>
-      <c r="BC9" s="38">
+      <c r="BC9" s="35">
         <v>50</v>
       </c>
-      <c r="BD9" s="38">
+      <c r="BD9" s="35">
         <v>465</v>
       </c>
       <c r="BE9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:58">
       <c r="A10">
         <v>2019</v>
       </c>
@@ -6523,29 +6487,29 @@
       <c r="C10" s="2">
         <v>44244</v>
       </c>
-      <c r="D10" s="24" t="s">
-        <v>73</v>
+      <c r="D10" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F10" s="2">
         <v>24240</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>59.791666666666664</v>
+        <v>59.8</v>
       </c>
       <c r="H10" s="5">
         <v>30.61</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K10" s="17">
+        <v>46</v>
+      </c>
+      <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" s="3">
@@ -6573,7 +6537,7 @@
         <v>1</v>
       </c>
       <c r="U10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V10" s="3">
         <v>0</v>
@@ -6621,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AL10" s="3">
         <v>2</v>
@@ -6630,49 +6594,49 @@
         <v>0</v>
       </c>
       <c r="AN10" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="AO10" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AP10" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="AQ10">
         <v>0</v>
       </c>
-      <c r="AR10" s="37">
+      <c r="AR10" s="34">
         <v>45054</v>
       </c>
-      <c r="AS10" s="38" t="s">
-        <v>57</v>
+      <c r="AS10" s="35" t="s">
+        <v>54</v>
       </c>
       <c r="AW10">
         <v>0</v>
       </c>
-      <c r="AX10" s="38">
+      <c r="AX10" s="35">
         <v>0</v>
       </c>
       <c r="AZ10">
         <v>0</v>
       </c>
-      <c r="BA10" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB10" s="38">
+      <c r="BA10" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="35">
         <v>550</v>
       </c>
-      <c r="BC10" s="38">
+      <c r="BC10" s="35">
         <v>200</v>
       </c>
-      <c r="BD10" s="38">
+      <c r="BD10" s="35">
         <v>400</v>
       </c>
       <c r="BE10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:58">
       <c r="A11">
         <v>2020</v>
       </c>
@@ -6682,27 +6646,27 @@
       <c r="C11" s="2">
         <v>44105</v>
       </c>
-      <c r="D11" s="24" t="s">
-        <v>64</v>
+      <c r="D11" s="23" t="s">
+        <v>61</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F11" s="2">
         <v>26926</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>52.44166666666667</v>
+        <v>52.45</v>
       </c>
       <c r="H11" s="5">
         <v>30.72</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -6716,11 +6680,11 @@
       <c r="O11" s="3">
         <v>0</v>
       </c>
-      <c r="P11" s="35">
+      <c r="P11" s="3">
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="R11" s="3">
         <v>1</v>
@@ -6732,7 +6696,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V11" s="3">
         <v>0</v>
@@ -6741,47 +6705,47 @@
         <v>1</v>
       </c>
       <c r="X11" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK11" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="Y11" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z11" s="20">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="3">
-        <v>1</v>
-      </c>
-      <c r="AI11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="3">
-        <v>1</v>
-      </c>
-      <c r="AK11" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="AL11" s="3">
         <v>0</v>
       </c>
@@ -6789,58 +6753,58 @@
         <v>0</v>
       </c>
       <c r="AN11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO11" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>166</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="34">
+        <v>44992</v>
+      </c>
+      <c r="AS11" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT11" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="AU11" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="35">
+        <v>1</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>167</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="35">
+        <v>750</v>
+      </c>
+      <c r="BC11" s="35">
         <v>100</v>
       </c>
-      <c r="AO11" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>171</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="37">
-        <v>44992</v>
-      </c>
-      <c r="AS11" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT11" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="AU11" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11" s="38">
-        <v>1</v>
-      </c>
-      <c r="AY11" t="s">
-        <v>172</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB11" s="38">
+      <c r="BD11" s="35">
         <v>750</v>
       </c>
-      <c r="BC11" s="38">
-        <v>100</v>
-      </c>
-      <c r="BD11" s="38">
-        <v>750</v>
-      </c>
       <c r="BE11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:58">
       <c r="A12">
         <v>2019</v>
       </c>
@@ -6850,27 +6814,27 @@
       <c r="C12" s="2">
         <v>44383</v>
       </c>
-      <c r="D12" s="24" t="s">
-        <v>73</v>
+      <c r="D12" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F12" s="2">
         <v>34325</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>32.18333333333333</v>
+        <v>32.19166666666667</v>
       </c>
       <c r="H12" s="5">
         <v>20.9</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -6884,14 +6848,14 @@
       <c r="O12" s="3">
         <v>0</v>
       </c>
-      <c r="P12" s="35">
+      <c r="P12" s="3">
         <v>0</v>
       </c>
       <c r="Q12" s="3">
         <v>0</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="S12" s="3">
         <v>1</v>
@@ -6900,7 +6864,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V12" s="3">
         <v>1</v>
@@ -6948,7 +6912,7 @@
         <v>1</v>
       </c>
       <c r="AK12" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AL12" s="3">
         <v>2</v>
@@ -6957,61 +6921,61 @@
         <v>1</v>
       </c>
       <c r="AN12" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="AO12" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>173</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="34">
+        <v>45512</v>
+      </c>
+      <c r="AS12" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT12" s="35" t="s">
+        <v>260</v>
+      </c>
+      <c r="AU12" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="AV12" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="AP12" t="s">
-        <v>180</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="37">
-        <v>45512</v>
-      </c>
-      <c r="AS12" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT12" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="AU12" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="AV12" s="38" t="s">
-        <v>184</v>
-      </c>
       <c r="AW12">
         <v>0</v>
       </c>
-      <c r="AX12" s="38">
+      <c r="AX12" s="35">
         <v>1</v>
       </c>
       <c r="AY12" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="AZ12">
         <v>1</v>
       </c>
-      <c r="BA12" s="38">
-        <v>1</v>
-      </c>
-      <c r="BB12" s="38">
+      <c r="BA12" s="35">
+        <v>1</v>
+      </c>
+      <c r="BB12" s="35">
         <v>350</v>
       </c>
-      <c r="BC12" s="38">
+      <c r="BC12" s="35">
         <v>50</v>
       </c>
-      <c r="BD12" s="38" t="s">
-        <v>182</v>
+      <c r="BD12" s="35" t="s">
+        <v>175</v>
       </c>
       <c r="BE12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:58">
       <c r="A13">
         <v>2020</v>
       </c>
@@ -7021,27 +6985,27 @@
       <c r="C13" s="2">
         <v>44134</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>73</v>
+      <c r="D13" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F13" s="2">
         <v>29223</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>46.152777777777779</v>
+        <v>46.161111111111111</v>
       </c>
       <c r="H13" s="5">
         <v>23.96</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -7059,7 +7023,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="R13" s="3">
         <v>0</v>
@@ -7071,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V13" s="3">
         <v>1</v>
@@ -7119,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AL13" s="3">
         <v>0</v>
@@ -7128,49 +7092,49 @@
         <v>0</v>
       </c>
       <c r="AN13" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="AO13" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>180</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="34">
+        <v>45331</v>
+      </c>
+      <c r="AS13" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="35">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB13" s="35">
+        <v>350</v>
+      </c>
+      <c r="BC13" s="35">
+        <v>60</v>
+      </c>
+      <c r="BD13" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="AO13" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="AP13" t="s">
-        <v>187</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="37">
-        <v>45331</v>
-      </c>
-      <c r="AS13" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13" s="38">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB13" s="38">
-        <v>350</v>
-      </c>
-      <c r="BC13" s="38">
-        <v>60</v>
-      </c>
-      <c r="BD13" s="38" t="s">
-        <v>185</v>
-      </c>
       <c r="BE13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:58">
       <c r="A14">
         <v>2020</v>
       </c>
@@ -7180,27 +7144,27 @@
       <c r="C14" s="2">
         <v>409506</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>73</v>
+      <c r="D14" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F14" s="2">
         <v>31562</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>39.744444444444447</v>
+        <v>39.75277777777778</v>
       </c>
       <c r="H14" s="5">
         <v>19.309999999999999</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -7227,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V14" s="3">
         <v>1</v>
@@ -7275,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AL14" s="3">
         <v>2</v>
@@ -7284,55 +7248,55 @@
         <v>0</v>
       </c>
       <c r="AN14" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="AO14" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AP14" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AQ14">
         <v>0</v>
       </c>
-      <c r="AR14" s="37">
+      <c r="AR14" s="34">
         <v>44411</v>
       </c>
-      <c r="AS14" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT14" s="38" t="s">
-        <v>246</v>
+      <c r="AS14" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT14" s="35" t="s">
+        <v>239</v>
       </c>
       <c r="AW14">
         <v>1</v>
       </c>
-      <c r="AX14" s="38">
+      <c r="AX14" s="35">
         <v>1</v>
       </c>
       <c r="AY14" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="AZ14">
         <v>1</v>
       </c>
-      <c r="BA14" s="38">
-        <v>1</v>
-      </c>
-      <c r="BB14" s="38">
+      <c r="BA14" s="35">
+        <v>1</v>
+      </c>
+      <c r="BB14" s="35">
         <v>350</v>
       </c>
-      <c r="BC14" s="38">
-        <v>0</v>
-      </c>
-      <c r="BD14" s="38">
+      <c r="BC14" s="35">
+        <v>0</v>
+      </c>
+      <c r="BD14" s="35">
         <v>365</v>
       </c>
       <c r="BE14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:58">
       <c r="A15">
         <v>2020</v>
       </c>
@@ -7342,27 +7306,27 @@
       <c r="C15" s="2">
         <v>44117</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>73</v>
+      <c r="D15" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F15" s="2">
         <v>27291</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>51.44166666666667</v>
+        <v>51.45</v>
       </c>
       <c r="H15" s="5">
         <v>18.54</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -7392,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V15" s="3">
         <v>1</v>
@@ -7427,7 +7391,7 @@
       <c r="AF15" s="3">
         <v>1</v>
       </c>
-      <c r="AG15" s="43">
+      <c r="AG15" s="40">
         <v>0</v>
       </c>
       <c r="AH15" s="3">
@@ -7440,7 +7404,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AL15" s="3">
         <v>2</v>
@@ -7449,52 +7413,52 @@
         <v>1</v>
       </c>
       <c r="AN15" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AO15" s="6" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="AP15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="AQ15">
         <v>0</v>
       </c>
-      <c r="AR15" s="37">
+      <c r="AR15" s="34">
         <v>45992</v>
       </c>
-      <c r="AS15" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT15" s="38" t="s">
-        <v>266</v>
+      <c r="AS15" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="AT15" s="35" t="s">
+        <v>255</v>
       </c>
       <c r="AW15">
         <v>0</v>
       </c>
-      <c r="AX15" s="38">
+      <c r="AX15" s="35">
         <v>0</v>
       </c>
       <c r="AZ15">
         <v>0</v>
       </c>
-      <c r="BA15" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB15" s="38">
+      <c r="BA15" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB15" s="35">
         <v>350</v>
       </c>
-      <c r="BC15" s="38">
+      <c r="BC15" s="35">
         <v>50</v>
       </c>
-      <c r="BD15" s="38">
+      <c r="BD15" s="35">
         <v>330</v>
       </c>
       <c r="BE15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:58">
       <c r="A16">
         <v>2019</v>
       </c>
@@ -7504,27 +7468,27 @@
       <c r="C16" s="2">
         <v>44084</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>73</v>
+      <c r="D16" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F16" s="2">
         <v>28651</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>47.716666666666669</v>
+        <v>47.725000000000001</v>
       </c>
       <c r="H16" s="5">
         <v>24.34</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -7554,7 +7518,7 @@
         <v>1</v>
       </c>
       <c r="U16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V16" s="3">
         <v>0</v>
@@ -7602,7 +7566,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AL16" s="3">
         <v>2</v>
@@ -7614,55 +7578,55 @@
         <v>0</v>
       </c>
       <c r="AO16" s="6" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="AP16" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AQ16">
         <v>0</v>
       </c>
-      <c r="AR16" s="37">
+      <c r="AR16" s="34">
         <v>45782</v>
       </c>
-      <c r="AS16" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT16" s="38" t="s">
-        <v>160</v>
+      <c r="AS16" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT16" s="35" t="s">
+        <v>155</v>
       </c>
       <c r="AW16">
         <v>0</v>
       </c>
-      <c r="AX16" s="38">
+      <c r="AX16" s="35">
         <v>1</v>
       </c>
       <c r="AY16" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AZ16">
         <v>1</v>
       </c>
-      <c r="BA16" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB16" s="38">
+      <c r="BA16" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB16" s="35">
         <v>550</v>
       </c>
-      <c r="BC16" s="38">
+      <c r="BC16" s="35">
         <v>400</v>
       </c>
-      <c r="BD16" s="38" t="s">
-        <v>196</v>
+      <c r="BD16" s="35" t="s">
+        <v>189</v>
       </c>
       <c r="BE16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="BF16" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:57">
       <c r="A17">
         <v>2020</v>
       </c>
@@ -7672,27 +7636,27 @@
       <c r="C17" s="2">
         <v>44196</v>
       </c>
-      <c r="D17" s="24" t="s">
-        <v>64</v>
+      <c r="D17" s="23" t="s">
+        <v>61</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F17" s="2">
         <v>19534</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>72.677777777777777</v>
+        <v>72.686111111111117</v>
       </c>
       <c r="H17" s="5">
         <v>30.86</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -7710,7 +7674,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="R17" s="3">
         <v>1</v>
@@ -7722,7 +7686,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V17" s="3">
         <v>0</v>
@@ -7757,7 +7721,7 @@
       <c r="AF17" s="3">
         <v>1</v>
       </c>
-      <c r="AG17" s="43">
+      <c r="AG17" s="40">
         <v>0</v>
       </c>
       <c r="AH17" s="3">
@@ -7770,7 +7734,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="AL17" s="3">
         <v>1</v>
@@ -7782,46 +7746,46 @@
         <v>0</v>
       </c>
       <c r="AO17" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="AP17" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AQ17">
         <v>0</v>
       </c>
-      <c r="AR17" s="37">
+      <c r="AR17" s="34">
         <v>45874</v>
       </c>
-      <c r="AS17" s="38" t="s">
-        <v>57</v>
+      <c r="AS17" s="35" t="s">
+        <v>54</v>
       </c>
       <c r="AW17">
         <v>0</v>
       </c>
-      <c r="AX17" s="38">
+      <c r="AX17" s="35">
         <v>0</v>
       </c>
       <c r="AZ17">
         <v>0</v>
       </c>
-      <c r="BA17" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB17" s="38">
+      <c r="BA17" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB17" s="35">
         <v>750</v>
       </c>
-      <c r="BC17" s="38">
+      <c r="BC17" s="35">
         <v>50</v>
       </c>
-      <c r="BD17" s="38">
+      <c r="BD17" s="35">
         <v>770</v>
       </c>
       <c r="BE17" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:57">
       <c r="A18">
         <v>2020</v>
       </c>
@@ -7831,27 +7795,27 @@
       <c r="C18" s="2">
         <v>44144</v>
       </c>
-      <c r="D18" s="24" t="s">
-        <v>64</v>
+      <c r="D18" s="23" t="s">
+        <v>61</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F18" s="2">
         <v>17617</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>77.924999999999997</v>
+        <v>77.933333333333337</v>
       </c>
       <c r="H18" s="5">
         <v>26.85</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -7872,7 +7836,7 @@
         <v>0</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="S18" s="3">
         <v>1</v>
@@ -7881,7 +7845,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V18" s="3">
         <v>0</v>
@@ -7929,64 +7893,64 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="3">
+        <v>1</v>
+      </c>
+      <c r="AN18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO18" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>197</v>
+      </c>
+      <c r="AR18" s="34">
+        <v>45071</v>
+      </c>
+      <c r="AS18" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="AL18" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM18" s="3">
-        <v>1</v>
-      </c>
-      <c r="AN18" s="3" t="s">
+      <c r="AT18" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="AU18" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="AO18" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="AP18" t="s">
-        <v>204</v>
-      </c>
-      <c r="AR18" s="37">
-        <v>45071</v>
-      </c>
-      <c r="AS18" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT18" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="AU18" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="AV18" s="38" t="s">
-        <v>153</v>
+      <c r="AV18" s="35" t="s">
+        <v>148</v>
       </c>
       <c r="AW18">
         <v>1</v>
       </c>
-      <c r="AX18" s="41">
+      <c r="AX18" s="38">
         <v>1</v>
       </c>
       <c r="AZ18">
         <v>0</v>
       </c>
-      <c r="BA18" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB18" s="38">
+      <c r="BA18" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB18" s="35">
         <v>500</v>
       </c>
-      <c r="BC18" s="38">
+      <c r="BC18" s="35">
         <v>100</v>
       </c>
-      <c r="BD18" s="38">
+      <c r="BD18" s="35">
         <v>300</v>
       </c>
       <c r="BE18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:57">
       <c r="A19">
         <v>2020</v>
       </c>
@@ -7996,35 +7960,34 @@
       <c r="C19" s="2">
         <v>44292</v>
       </c>
-      <c r="D19" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>207</v>
+      <c r="D19" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="E19" t="s">
+        <v>200</v>
       </c>
       <c r="F19" s="2">
         <v>28642</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>47.741666666666667</v>
+        <v>47.75</v>
       </c>
       <c r="H19" s="5">
         <v>22.43</v>
       </c>
-      <c r="I19" s="17" t="s">
-        <v>48</v>
+      <c r="I19" t="s">
+        <v>45</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K19" s="17">
+        <v>46</v>
+      </c>
+      <c r="K19">
         <v>0</v>
       </c>
       <c r="L19" s="3">
         <v>0</v>
       </c>
-      <c r="M19" s="17"/>
       <c r="N19" s="3">
         <v>0</v>
       </c>
@@ -8047,7 +8010,7 @@
         <v>1</v>
       </c>
       <c r="U19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V19" s="3">
         <v>0</v>
@@ -8056,10 +8019,10 @@
         <v>1</v>
       </c>
       <c r="X19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Y19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Z19" s="3">
         <v>1</v>
@@ -8082,7 +8045,7 @@
       <c r="AF19" s="3">
         <v>1</v>
       </c>
-      <c r="AG19" s="43">
+      <c r="AG19" s="40">
         <v>0</v>
       </c>
       <c r="AH19" s="3">
@@ -8095,7 +8058,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AL19" s="3">
         <v>2</v>
@@ -8104,49 +8067,49 @@
         <v>1</v>
       </c>
       <c r="AN19" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="AO19" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="AP19" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="AQ19">
         <v>0</v>
       </c>
-      <c r="AR19" s="37">
+      <c r="AR19" s="34">
         <v>44726</v>
       </c>
-      <c r="AS19" s="38" t="s">
-        <v>57</v>
+      <c r="AS19" s="35" t="s">
+        <v>54</v>
       </c>
       <c r="AW19">
         <v>0</v>
       </c>
-      <c r="AX19" s="38">
+      <c r="AX19" s="35">
         <v>0</v>
       </c>
       <c r="AZ19">
         <v>0</v>
       </c>
-      <c r="BA19" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB19" s="38">
+      <c r="BA19" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB19" s="35">
         <v>450</v>
       </c>
-      <c r="BC19" s="38">
+      <c r="BC19" s="35">
         <v>150</v>
       </c>
-      <c r="BD19" s="38">
+      <c r="BD19" s="35">
         <v>485</v>
       </c>
       <c r="BE19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:57">
       <c r="A20">
         <v>2020</v>
       </c>
@@ -8156,27 +8119,27 @@
       <c r="C20" s="2">
         <v>44258</v>
       </c>
-      <c r="D20" s="24" t="s">
-        <v>257</v>
+      <c r="D20" s="23" t="s">
+        <v>250</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F20" s="2">
         <v>16837</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>80.066666666666663</v>
+        <v>80.075000000000003</v>
       </c>
       <c r="H20" s="5">
         <v>33.020000000000003</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -8197,7 +8160,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="R20" s="3">
         <v>1</v>
@@ -8209,7 +8172,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V20" s="3">
         <v>1</v>
@@ -8257,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="AL20" s="3">
         <v>1</v>
@@ -8269,51 +8232,51 @@
         <v>0</v>
       </c>
       <c r="AO20" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AP20" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="AQ20">
         <v>0</v>
       </c>
-      <c r="AR20" s="37">
+      <c r="AR20" s="34">
         <v>45993</v>
       </c>
-      <c r="AS20" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT20" s="38" t="s">
-        <v>273</v>
+      <c r="AS20" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="AT20" s="35" t="s">
+        <v>262</v>
       </c>
       <c r="AW20">
         <v>0</v>
       </c>
-      <c r="AX20" s="38">
+      <c r="AX20" s="35">
         <v>0</v>
       </c>
       <c r="AZ20">
         <v>0</v>
       </c>
-      <c r="BA20" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB20" s="38">
+      <c r="BA20" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB20" s="35">
         <v>650</v>
       </c>
-      <c r="BC20" s="38">
+      <c r="BC20" s="35">
         <v>200</v>
       </c>
-      <c r="BD20" s="38">
+      <c r="BD20" s="35">
         <v>560</v>
       </c>
       <c r="BE20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:57">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B21" s="2">
         <v>44113</v>
@@ -8321,27 +8284,27 @@
       <c r="C21" s="2">
         <v>44167</v>
       </c>
-      <c r="D21" s="24" t="s">
-        <v>254</v>
+      <c r="D21" s="23" t="s">
+        <v>247</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F21" s="2">
         <v>27665</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>50.416666666666664</v>
+        <v>50.424999999999997</v>
       </c>
       <c r="H21" s="5">
         <v>18.989999999999998</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -8371,7 +8334,7 @@
         <v>1</v>
       </c>
       <c r="U21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V21" s="3">
         <v>0</v>
@@ -8406,85 +8369,85 @@
       <c r="AF21" s="3">
         <v>0</v>
       </c>
-      <c r="AG21" s="43">
+      <c r="AG21" s="40">
         <v>0</v>
       </c>
       <c r="AH21" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AI21" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AJ21" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AK21" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AL21" s="3">
         <v>2</v>
       </c>
-      <c r="AM21" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="AN21" s="26" t="s">
-        <v>115</v>
+      <c r="AM21" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="AN21" s="25" t="s">
+        <v>111</v>
       </c>
       <c r="AO21" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AP21" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AQ21">
         <v>0</v>
       </c>
-      <c r="AR21" s="37">
+      <c r="AR21" s="34">
         <v>45106</v>
       </c>
-      <c r="AS21" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT21" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="AU21" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="AV21" s="38" t="s">
-        <v>274</v>
+      <c r="AS21" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT21" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU21" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="AV21" s="35" t="s">
+        <v>263</v>
       </c>
       <c r="AW21">
         <v>0</v>
       </c>
-      <c r="AX21" s="38">
+      <c r="AX21" s="35">
         <v>1</v>
       </c>
       <c r="AY21" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AZ21">
         <v>0</v>
       </c>
-      <c r="BA21" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB21" s="38">
+      <c r="BA21" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB21" s="35">
         <v>275</v>
       </c>
-      <c r="BC21" s="38">
+      <c r="BC21" s="35">
         <v>100</v>
       </c>
-      <c r="BD21" s="38">
+      <c r="BD21" s="35">
         <v>275</v>
       </c>
       <c r="BE21" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:57">
       <c r="A22" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B22" s="2">
         <v>44148</v>
@@ -8492,27 +8455,27 @@
       <c r="C22" s="2">
         <v>44217</v>
       </c>
-      <c r="D22" s="24" t="s">
-        <v>254</v>
+      <c r="D22" s="23" t="s">
+        <v>247</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F22" s="2">
         <v>34886</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>30.644444444444446</v>
+        <v>30.652777777777779</v>
       </c>
       <c r="H22" s="5">
         <v>22.5</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -8530,7 +8493,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="R22" s="3">
         <v>1</v>
@@ -8542,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V22" s="3">
         <v>1</v>
@@ -8574,74 +8537,74 @@
       <c r="AE22" s="3">
         <v>1</v>
       </c>
-      <c r="AF22" s="26">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="26">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI22" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="AJ22" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="AK22" s="26" t="s">
-        <v>115</v>
+      <c r="AF22" s="25">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="25">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="AI22" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="AJ22" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK22" s="25" t="s">
+        <v>111</v>
       </c>
       <c r="AL22" s="3">
         <v>2</v>
       </c>
-      <c r="AM22" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="AN22" s="26" t="s">
-        <v>115</v>
+      <c r="AM22" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="AN22" s="25" t="s">
+        <v>111</v>
       </c>
       <c r="AO22" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AP22" s="16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AQ22">
         <v>0</v>
       </c>
-      <c r="AR22" s="37">
+      <c r="AR22" s="34">
         <v>44580</v>
       </c>
-      <c r="AS22" s="38" t="s">
-        <v>57</v>
+      <c r="AS22" s="35" t="s">
+        <v>54</v>
       </c>
       <c r="AW22">
         <v>0</v>
       </c>
-      <c r="AX22" s="38">
+      <c r="AX22" s="35">
         <v>0</v>
       </c>
       <c r="AZ22">
         <v>0</v>
       </c>
-      <c r="BA22" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB22" s="38">
+      <c r="BA22" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB22" s="35">
         <v>300</v>
       </c>
-      <c r="BC22" s="38">
-        <v>0</v>
-      </c>
-      <c r="BD22" s="38">
+      <c r="BC22" s="35">
+        <v>0</v>
+      </c>
+      <c r="BD22" s="35">
         <v>310</v>
       </c>
       <c r="BE22" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:57">
       <c r="A23">
         <v>2020</v>
       </c>
@@ -8651,27 +8614,27 @@
       <c r="C23" s="2">
         <v>44202</v>
       </c>
-      <c r="D23" s="24" t="s">
-        <v>73</v>
+      <c r="D23" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F23" s="2">
         <v>28867</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>47.12777777777778</v>
+        <v>47.136111111111113</v>
       </c>
       <c r="H23" s="5">
         <v>26</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -8689,7 +8652,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="R23" s="3">
         <v>1</v>
@@ -8701,7 +8664,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V23" s="3">
         <v>0</v>
@@ -8736,7 +8699,7 @@
       <c r="AF23" s="3">
         <v>1</v>
       </c>
-      <c r="AG23" s="35">
+      <c r="AG23" s="3">
         <v>0</v>
       </c>
       <c r="AH23" s="3">
@@ -8749,7 +8712,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AL23" s="3">
         <v>2</v>
@@ -8757,53 +8720,53 @@
       <c r="AM23" s="3">
         <v>0</v>
       </c>
-      <c r="AN23" s="27" t="s">
-        <v>100</v>
+      <c r="AN23" s="26" t="s">
+        <v>96</v>
       </c>
       <c r="AO23" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AP23" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="AQ23">
         <v>0</v>
       </c>
-      <c r="AR23" s="37">
+      <c r="AR23" s="34">
         <v>45972</v>
       </c>
-      <c r="AS23" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT23" s="38" t="s">
-        <v>266</v>
+      <c r="AS23" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="AT23" s="35" t="s">
+        <v>255</v>
       </c>
       <c r="AW23">
         <v>0</v>
       </c>
-      <c r="AX23" s="38">
+      <c r="AX23" s="35">
         <v>0</v>
       </c>
       <c r="AZ23">
         <v>0</v>
       </c>
-      <c r="BA23" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB23" s="38">
+      <c r="BA23" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB23" s="35">
         <v>600</v>
       </c>
-      <c r="BC23" s="38">
+      <c r="BC23" s="35">
         <v>200</v>
       </c>
-      <c r="BD23" s="38">
+      <c r="BD23" s="35">
         <v>605</v>
       </c>
       <c r="BE23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:57">
       <c r="A24">
         <v>2020</v>
       </c>
@@ -8813,27 +8776,27 @@
       <c r="C24" s="2">
         <v>44344</v>
       </c>
-      <c r="D24" s="24" t="s">
-        <v>256</v>
+      <c r="D24" s="23" t="s">
+        <v>249</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F24" s="2">
         <v>23180</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>62.694444444444443</v>
+        <v>62.702777777777776</v>
       </c>
       <c r="H24" s="5">
         <v>28.15</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -8863,7 +8826,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V24" s="3">
         <v>1</v>
@@ -8898,7 +8861,7 @@
       <c r="AF24" s="3">
         <v>1</v>
       </c>
-      <c r="AG24" s="20">
+      <c r="AG24" s="19">
         <v>1</v>
       </c>
       <c r="AH24" s="3">
@@ -8911,7 +8874,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AL24" s="3">
         <v>2</v>
@@ -8919,56 +8882,56 @@
       <c r="AM24" s="3">
         <v>0</v>
       </c>
-      <c r="AN24" s="27" t="s">
-        <v>227</v>
+      <c r="AN24" s="26" t="s">
+        <v>220</v>
       </c>
       <c r="AO24" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AP24" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="AQ24">
         <v>0</v>
       </c>
-      <c r="AR24" s="37">
+      <c r="AR24" s="34">
         <v>45397</v>
       </c>
-      <c r="AS24" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT24" s="38" t="s">
-        <v>217</v>
+      <c r="AS24" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT24" s="35" t="s">
+        <v>210</v>
       </c>
       <c r="AW24">
         <v>0</v>
       </c>
-      <c r="AX24" s="38">
+      <c r="AX24" s="35">
         <v>1</v>
       </c>
       <c r="AY24" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="AZ24">
         <v>1</v>
       </c>
-      <c r="BA24" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="BB24" s="38">
+      <c r="BA24" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="BB24" s="35">
         <v>750</v>
       </c>
-      <c r="BC24" s="38">
+      <c r="BC24" s="35">
         <v>200</v>
       </c>
-      <c r="BD24" s="38">
+      <c r="BD24" s="35">
         <v>605</v>
       </c>
       <c r="BE24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:57">
       <c r="A25">
         <v>2020</v>
       </c>
@@ -8978,27 +8941,27 @@
       <c r="C25" s="2">
         <v>44404</v>
       </c>
-      <c r="D25" s="24" t="s">
-        <v>73</v>
+      <c r="D25" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F25" s="2">
         <v>15710</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>83.15</v>
+        <v>83.158333333333331</v>
       </c>
       <c r="H25" s="5">
         <v>22.67</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -9028,7 +8991,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V25" s="3">
         <v>0</v>
@@ -9042,7 +9005,7 @@
       <c r="Y25">
         <v>1</v>
       </c>
-      <c r="Z25" s="20">
+      <c r="Z25" s="19">
         <v>0</v>
       </c>
       <c r="AA25" s="3">
@@ -9063,7 +9026,7 @@
       <c r="AF25" s="3">
         <v>1</v>
       </c>
-      <c r="AG25" s="20">
+      <c r="AG25" s="19">
         <v>1</v>
       </c>
       <c r="AH25" s="3">
@@ -9076,7 +9039,7 @@
         <v>1</v>
       </c>
       <c r="AK25" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AL25" s="3">
         <v>0</v>
@@ -9085,49 +9048,49 @@
         <v>0</v>
       </c>
       <c r="AN25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO25" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="AP25" t="s">
+        <v>215</v>
+      </c>
+      <c r="AR25" s="34">
+        <v>45790</v>
+      </c>
+      <c r="AS25" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="AT25" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="AW25">
+        <v>1</v>
+      </c>
+      <c r="AX25" s="35">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB25" s="35">
+        <v>500</v>
+      </c>
+      <c r="BC25" s="35">
         <v>100</v>
       </c>
-      <c r="AO25" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="AP25" t="s">
-        <v>222</v>
-      </c>
-      <c r="AR25" s="37">
-        <v>45790</v>
-      </c>
-      <c r="AS25" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT25" s="38" t="s">
-        <v>251</v>
-      </c>
-      <c r="AW25">
-        <v>1</v>
-      </c>
-      <c r="AX25" s="38">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB25" s="38">
-        <v>500</v>
-      </c>
-      <c r="BC25" s="38">
-        <v>100</v>
-      </c>
-      <c r="BD25" s="38">
+      <c r="BD25" s="35">
         <v>405</v>
       </c>
       <c r="BE25" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:57">
       <c r="A26">
         <v>2019</v>
       </c>
@@ -9137,27 +9100,27 @@
       <c r="C26" s="2">
         <v>44244</v>
       </c>
-      <c r="D26" s="24" t="s">
-        <v>73</v>
+      <c r="D26" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F26" s="2">
         <v>24240</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>59.791666666666664</v>
+        <v>59.8</v>
       </c>
       <c r="H26" s="5">
         <v>30.61</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -9187,7 +9150,7 @@
         <v>1</v>
       </c>
       <c r="U26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V26" s="3">
         <v>0</v>
@@ -9222,7 +9185,7 @@
       <c r="AF26" s="3">
         <v>1</v>
       </c>
-      <c r="AG26" s="35">
+      <c r="AG26" s="3">
         <v>0</v>
       </c>
       <c r="AH26" s="3">
@@ -9235,7 +9198,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AL26" s="3">
         <v>2</v>
@@ -9243,53 +9206,53 @@
       <c r="AM26" s="3">
         <v>0</v>
       </c>
-      <c r="AN26" s="27">
+      <c r="AN26" s="26">
         <v>0</v>
       </c>
       <c r="AO26" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="AP26" s="6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AQ26">
         <v>0</v>
       </c>
-      <c r="AR26" s="37">
+      <c r="AR26" s="34">
         <v>45054</v>
       </c>
-      <c r="AS26" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT26" s="42" t="s">
-        <v>70</v>
+      <c r="AS26" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="AT26" s="39" t="s">
+        <v>67</v>
       </c>
       <c r="AW26">
         <v>0</v>
       </c>
-      <c r="AX26" s="38">
+      <c r="AX26" s="35">
         <v>0</v>
       </c>
       <c r="AZ26">
         <v>0</v>
       </c>
-      <c r="BA26" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB26" s="38">
+      <c r="BA26" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB26" s="35">
         <v>550</v>
       </c>
-      <c r="BC26" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="BD26" s="38">
+      <c r="BC26" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="BD26" s="35">
         <v>400</v>
       </c>
       <c r="BE26" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:57">
       <c r="A27">
         <v>2020</v>
       </c>
@@ -9299,27 +9262,27 @@
       <c r="C27" s="2">
         <v>44337</v>
       </c>
-      <c r="D27" s="24" t="s">
-        <v>73</v>
+      <c r="D27" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F27" s="2">
         <v>27346</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>51.291666666666664</v>
+        <v>51.3</v>
       </c>
       <c r="H27" s="5">
         <v>26.28</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -9337,7 +9300,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="R27" s="3">
         <v>1</v>
@@ -9349,7 +9312,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V27" s="3">
         <v>0</v>
@@ -9384,7 +9347,7 @@
       <c r="AF27" s="3">
         <v>1</v>
       </c>
-      <c r="AG27" s="44">
+      <c r="AG27" s="41">
         <v>0</v>
       </c>
       <c r="AH27" s="3">
@@ -9397,7 +9360,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AL27" s="3">
         <v>2</v>
@@ -9405,56 +9368,56 @@
       <c r="AM27" s="3">
         <v>1</v>
       </c>
-      <c r="AN27" s="27" t="s">
-        <v>227</v>
+      <c r="AN27" s="26" t="s">
+        <v>220</v>
       </c>
       <c r="AO27" s="6" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="AP27" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AQ27">
         <v>0</v>
       </c>
-      <c r="AR27" s="37">
+      <c r="AR27" s="34">
         <v>44659</v>
       </c>
-      <c r="AS27" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="AT27" s="38" t="s">
-        <v>251</v>
-      </c>
-      <c r="AU27" s="38" t="s">
-        <v>104</v>
+      <c r="AS27" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="AT27" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="AU27" s="35" t="s">
+        <v>100</v>
       </c>
       <c r="AW27">
         <v>1</v>
       </c>
-      <c r="AX27" s="38">
+      <c r="AX27" s="35">
         <v>0</v>
       </c>
       <c r="AZ27">
         <v>0</v>
       </c>
-      <c r="BA27" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB27" s="38">
+      <c r="BA27" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB27" s="35">
         <v>600</v>
       </c>
-      <c r="BC27" s="38">
+      <c r="BC27" s="35">
         <v>50</v>
       </c>
-      <c r="BD27" s="38">
+      <c r="BD27" s="35">
         <v>605</v>
       </c>
       <c r="BE27" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:57">
       <c r="A28">
         <v>2020</v>
       </c>
@@ -9464,27 +9427,27 @@
       <c r="C28" s="2">
         <v>44355</v>
       </c>
-      <c r="D28" s="24" t="s">
-        <v>73</v>
+      <c r="D28" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F28" s="2">
         <v>30196</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>43.488888888888887</v>
+        <v>43.49722222222222</v>
       </c>
       <c r="H28" s="5">
         <v>27.84</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -9502,7 +9465,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="R28" s="3">
         <v>1</v>
@@ -9514,7 +9477,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="V28" s="3">
         <v>0</v>
@@ -9562,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AL28" s="3">
         <v>2</v>
@@ -9570,56 +9533,56 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
-      <c r="AN28" s="27" t="s">
-        <v>227</v>
+      <c r="AN28" s="26" t="s">
+        <v>220</v>
       </c>
       <c r="AO28" s="6" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="AP28" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="AQ28">
         <v>0</v>
       </c>
-      <c r="AR28" s="37">
+      <c r="AR28" s="34">
         <v>45860</v>
       </c>
-      <c r="AS28" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT28" s="38" t="s">
-        <v>183</v>
+      <c r="AS28" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT28" s="35" t="s">
+        <v>176</v>
       </c>
       <c r="AW28">
         <v>0</v>
       </c>
-      <c r="AX28" s="38">
+      <c r="AX28" s="35">
         <v>1</v>
       </c>
       <c r="AY28" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="AZ28">
         <v>0</v>
       </c>
-      <c r="BA28" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB28" s="38">
+      <c r="BA28" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB28" s="35">
         <v>750</v>
       </c>
-      <c r="BC28" s="38">
+      <c r="BC28" s="35">
         <v>50</v>
       </c>
-      <c r="BD28" s="38">
+      <c r="BD28" s="35">
         <v>800</v>
       </c>
       <c r="BE28" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:57">
       <c r="A29">
         <v>2020</v>
       </c>
@@ -9629,27 +9592,27 @@
       <c r="C29" s="2">
         <v>44438</v>
       </c>
-      <c r="D29" s="24" t="s">
-        <v>73</v>
+      <c r="D29" s="23" t="s">
+        <v>70</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F29" s="2">
         <v>30387</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>42.961111111111109</v>
+        <v>42.969444444444441</v>
       </c>
       <c r="H29" s="5">
         <v>27.25</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -9667,7 +9630,7 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="R29" s="3">
         <v>1</v>
@@ -9679,7 +9642,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V29" s="3">
         <v>1</v>
@@ -9714,7 +9677,7 @@
       <c r="AF29" s="3">
         <v>1</v>
       </c>
-      <c r="AG29" s="20">
+      <c r="AG29" s="19">
         <v>0</v>
       </c>
       <c r="AH29" s="3">
@@ -9727,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AL29" s="3">
         <v>2</v>
@@ -9735,50 +9698,50 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
-      <c r="AN29" s="27" t="s">
-        <v>100</v>
+      <c r="AN29" s="26" t="s">
+        <v>96</v>
       </c>
       <c r="AO29" s="6" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AP29" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="AQ29">
         <v>0</v>
       </c>
-      <c r="AR29" s="37">
+      <c r="AR29" s="34">
         <v>45237</v>
       </c>
-      <c r="AS29" s="38" t="s">
-        <v>57</v>
+      <c r="AS29" s="35" t="s">
+        <v>54</v>
       </c>
       <c r="AW29">
         <v>0</v>
       </c>
-      <c r="AX29" s="38">
+      <c r="AX29" s="35">
         <v>0</v>
       </c>
       <c r="AZ29">
         <v>0</v>
       </c>
-      <c r="BA29" s="38">
-        <v>0</v>
-      </c>
-      <c r="BB29" s="41">
+      <c r="BA29" s="35">
+        <v>0</v>
+      </c>
+      <c r="BB29" s="38">
         <v>600</v>
       </c>
-      <c r="BC29" s="38">
+      <c r="BC29" s="35">
         <v>280</v>
       </c>
-      <c r="BD29" s="38">
+      <c r="BD29" s="35">
         <v>605</v>
       </c>
       <c r="BE29" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:57">
       <c r="A30">
         <v>2019</v>
       </c>
@@ -9788,27 +9751,27 @@
       <c r="C30" s="2">
         <v>44123</v>
       </c>
-      <c r="D30" s="24" t="s">
-        <v>258</v>
+      <c r="D30" s="23" t="s">
+        <v>251</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F30" s="2">
         <v>24627</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>58.733333333333334</v>
+        <v>58.741666666666667</v>
       </c>
       <c r="H30" s="5">
         <v>19.13</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -9826,7 +9789,7 @@
         <v>0</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="R30" s="3">
         <v>0</v>
@@ -9838,7 +9801,7 @@
         <v>1</v>
       </c>
       <c r="U30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V30" s="3">
         <v>1</v>
@@ -9886,67 +9849,67 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO30" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="AP30" t="s">
+        <v>242</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30" s="34">
+        <v>45764</v>
+      </c>
+      <c r="AS30" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="AL30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN30" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="AO30" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="AP30" t="s">
-        <v>249</v>
-      </c>
-      <c r="AQ30">
-        <v>0</v>
-      </c>
-      <c r="AR30" s="37">
-        <v>45764</v>
-      </c>
-      <c r="AS30" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT30" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="AU30" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="AV30" s="38" t="s">
-        <v>66</v>
+      <c r="AT30" s="35" t="s">
+        <v>260</v>
+      </c>
+      <c r="AU30" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="AV30" s="35" t="s">
+        <v>63</v>
       </c>
       <c r="AW30">
         <v>1</v>
       </c>
-      <c r="AX30" s="38">
+      <c r="AX30" s="35">
         <v>1</v>
       </c>
       <c r="AY30" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AZ30">
         <v>1</v>
       </c>
-      <c r="BA30" s="38">
-        <v>1</v>
-      </c>
-      <c r="BB30" s="38">
+      <c r="BA30" s="35">
+        <v>1</v>
+      </c>
+      <c r="BB30" s="35">
         <v>250</v>
       </c>
-      <c r="BC30" s="38">
-        <v>0</v>
-      </c>
-      <c r="BD30" s="38">
+      <c r="BC30" s="35">
+        <v>0</v>
+      </c>
+      <c r="BD30" s="35">
         <v>170</v>
       </c>
       <c r="BE30" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dskin\Documents\Projects\propensity_score_matching\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9815A95A-852D-413C-9D2E-02A640BCDD98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE640C1B-1E33-4BDD-9785-03504315C490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14505" yWindow="-720" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{8D6ADBF5-96F6-B143-86A8-5692DBE5BF1C}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="263">
   <si>
     <t>dob</t>
   </si>
@@ -311,9 +311,6 @@
   </si>
   <si>
     <t xml:space="preserve">silicone </t>
-  </si>
-  <si>
-    <t>300 (R), 400 (L)</t>
   </si>
   <si>
     <t>III</t>
@@ -770,16 +767,10 @@
     <t>expander removal and debridement</t>
   </si>
   <si>
-    <t>275 (R) 295 (L)</t>
-  </si>
-  <si>
     <t>lymphedema</t>
   </si>
   <si>
     <t>capsulotomy and fat grafting</t>
-  </si>
-  <si>
-    <t>465 (R) 235 (L)</t>
   </si>
   <si>
     <r>
@@ -845,9 +836,6 @@
     <t>0.1 mm</t>
   </si>
   <si>
-    <t>300 (R) 400 (L)</t>
-  </si>
-  <si>
     <t>plan to swap for saline</t>
   </si>
   <si>
@@ -957,9 +945,6 @@
   </si>
   <si>
     <t>6mm x 2mm )(IDC), 9 cm DCIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 300 (R) 200 (L)</t>
   </si>
   <si>
     <r>
@@ -1787,7 +1772,7 @@
         <v>18</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>20</v>
@@ -1823,7 +1808,7 @@
         <v>78</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>6</v>
@@ -1841,7 +1826,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="V1" s="9" t="s">
         <v>41</v>
@@ -1853,19 +1838,19 @@
         <v>42</v>
       </c>
       <c r="Y1" s="9" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="Z1" s="9" t="s">
         <v>24</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AB1" s="9" t="s">
         <v>43</v>
       </c>
       <c r="AC1" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AD1" s="15" t="s">
         <v>11</v>
@@ -1874,7 +1859,7 @@
         <v>60</v>
       </c>
       <c r="AF1" s="9" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AG1" s="9" t="s">
         <v>28</v>
@@ -1954,14 +1939,14 @@
         <v>70</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" s="12">
         <v>28835</v>
       </c>
       <c r="F2" s="18">
         <f ca="1">YEARFRAC(E2,TODAY())</f>
-        <v>47.222222222222221</v>
+        <v>47.225000000000001</v>
       </c>
       <c r="G2" s="20">
         <v>20.09</v>
@@ -2049,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="AJ2" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK2" s="18">
         <v>2</v>
@@ -2058,13 +2043,13 @@
         <v>0</v>
       </c>
       <c r="AM2" s="32" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AP2" s="1">
         <v>0</v>
@@ -2076,7 +2061,7 @@
         <v>50</v>
       </c>
       <c r="AS2" s="27" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AT2" s="27"/>
       <c r="AU2" s="27"/>
@@ -2102,23 +2087,23 @@
     </row>
     <row r="3" spans="1:54">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B3" s="2">
         <v>43868</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E3" s="2">
         <v>30389</v>
       </c>
       <c r="F3" s="18">
         <f t="shared" ref="F3:F20" ca="1" si="0">YEARFRAC(E3,TODAY())</f>
-        <v>42.963888888888889</v>
+        <v>42.966666666666669</v>
       </c>
       <c r="G3" s="5">
         <v>24.72</v>
@@ -2191,22 +2176,22 @@
         <v>1</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AJ3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK3" s="3">
         <v>2</v>
@@ -2215,13 +2200,13 @@
         <v>0</v>
       </c>
       <c r="AM3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AO3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AP3">
         <v>0</v>
@@ -2233,7 +2218,7 @@
         <v>54</v>
       </c>
       <c r="AV3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AW3" s="28">
         <v>0</v>
@@ -2262,14 +2247,14 @@
         <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E4" s="2">
         <v>31680</v>
       </c>
       <c r="F4" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>39.43333333333333</v>
+        <v>39.43611111111111</v>
       </c>
       <c r="G4" s="5">
         <v>22.87</v>
@@ -2357,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK4" s="3">
         <v>2</v>
@@ -2366,13 +2351,13 @@
         <v>0</v>
       </c>
       <c r="AM4" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AO4" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AP4">
         <v>0</v>
@@ -2384,10 +2369,10 @@
         <v>50</v>
       </c>
       <c r="AS4" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AT4" s="28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AU4" s="28" t="s">
         <v>67</v>
@@ -2399,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="AX4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AY4">
         <v>1</v>
@@ -2422,17 +2407,17 @@
         <v>44048</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" s="2">
         <v>23434</v>
       </c>
       <c r="F5" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>62.011111111111113</v>
+        <v>62.013888888888886</v>
       </c>
       <c r="G5" s="5">
         <v>24.57</v>
@@ -2520,7 +2505,7 @@
         <v>0</v>
       </c>
       <c r="AJ5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK5" s="3">
         <v>1</v>
@@ -2529,13 +2514,13 @@
         <v>1</v>
       </c>
       <c r="AM5" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AN5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AO5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AP5">
         <v>0</v>
@@ -2547,19 +2532,19 @@
         <v>50</v>
       </c>
       <c r="AS5" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AT5" s="28" t="s">
         <v>63</v>
       </c>
       <c r="AV5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AW5" s="28">
         <v>1</v>
       </c>
       <c r="AX5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AY5">
         <v>1</v>
@@ -2579,17 +2564,17 @@
         <v>44127</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E6" s="2">
         <v>24739</v>
       </c>
       <c r="F6" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>58.43611111111111</v>
+        <v>58.43888888888889</v>
       </c>
       <c r="G6" s="5">
         <v>17.78</v>
@@ -2617,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q6" s="3">
         <v>1</v>
@@ -2668,31 +2653,31 @@
         <v>0</v>
       </c>
       <c r="AG6" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AH6" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AI6" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AJ6" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK6" s="3">
         <v>2</v>
       </c>
       <c r="AL6" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AM6" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AN6" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AO6" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AP6">
         <v>0</v>
@@ -2710,7 +2695,7 @@
         <v>1</v>
       </c>
       <c r="AX6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -2736,14 +2721,14 @@
         <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E7" s="2">
         <v>32050</v>
       </c>
       <c r="F7" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>38.419444444444444</v>
+        <v>38.422222222222224</v>
       </c>
       <c r="G7" s="5">
         <v>21.96</v>
@@ -2831,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK7" s="3">
         <v>2</v>
@@ -2840,13 +2825,13 @@
         <v>1</v>
       </c>
       <c r="AM7" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN7" t="s">
+        <v>126</v>
+      </c>
+      <c r="AO7" t="s">
         <v>127</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>128</v>
       </c>
       <c r="AP7">
         <v>0</v>
@@ -2858,7 +2843,7 @@
         <v>54</v>
       </c>
       <c r="AS7" s="28" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AV7">
         <v>0</v>
@@ -2881,23 +2866,23 @@
     </row>
     <row r="8" spans="1:54">
       <c r="A8" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="2">
         <v>44169</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2">
         <v>30752</v>
       </c>
       <c r="F8" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>41.972222222222221</v>
+        <v>41.975000000000001</v>
       </c>
       <c r="G8" s="5">
         <v>21.97</v>
@@ -2970,37 +2955,37 @@
         <v>1</v>
       </c>
       <c r="AE8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AH8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AI8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AJ8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK8" s="3">
         <v>2</v>
       </c>
       <c r="AL8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AM8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AN8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AO8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AP8">
         <v>0</v>
@@ -3015,13 +3000,13 @@
         <v>63</v>
       </c>
       <c r="AV8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AW8" s="28">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="s">
         <v>130</v>
-      </c>
-      <c r="AW8" s="28">
-        <v>1</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>131</v>
       </c>
       <c r="AY8">
         <v>0</v>
@@ -3047,14 +3032,14 @@
         <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E9" s="2">
         <v>34748</v>
       </c>
       <c r="F9" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>31.036111111111111</v>
+        <v>31.038888888888888</v>
       </c>
       <c r="G9" s="5">
         <v>22.31</v>
@@ -3142,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK9" s="3">
         <v>0</v>
@@ -3151,13 +3136,13 @@
         <v>0</v>
       </c>
       <c r="AM9" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AN9" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AO9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AP9">
         <v>0</v>
@@ -3195,17 +3180,17 @@
         <v>44141</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2">
         <v>23602</v>
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>61.55</v>
+        <v>61.552777777777777</v>
       </c>
       <c r="G10" s="5">
         <v>19.91</v>
@@ -3293,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK10" s="3">
         <v>2</v>
@@ -3305,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="AN10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AO10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AP10">
         <v>0</v>
@@ -3320,10 +3305,10 @@
         <v>54</v>
       </c>
       <c r="AS10" s="28" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AV10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AW10" s="28">
         <v>0</v>
@@ -3352,14 +3337,14 @@
         <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11" s="2">
         <v>31680</v>
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>39.43333333333333</v>
+        <v>39.43611111111111</v>
       </c>
       <c r="G11" s="5">
         <v>22.87</v>
@@ -3447,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="AJ11" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK11" s="3">
         <v>2</v>
@@ -3456,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="AM11" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN11" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO11" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="AO11" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="AP11">
         <v>0</v>
@@ -3474,10 +3459,10 @@
         <v>50</v>
       </c>
       <c r="AS11" s="28" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AT11" s="28" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AU11" s="28" t="s">
         <v>67</v>
@@ -3489,7 +3474,7 @@
         <v>1</v>
       </c>
       <c r="AX11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AY11">
         <v>1</v>
@@ -3501,7 +3486,7 @@
         <v>300</v>
       </c>
       <c r="BB11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:54">
@@ -3515,14 +3500,14 @@
         <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E12" s="2">
         <v>19447</v>
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>72.922222222222217</v>
+        <v>72.924999999999997</v>
       </c>
       <c r="G12" s="5">
         <v>19.13</v>
@@ -3618,13 +3603,13 @@
         <v>1</v>
       </c>
       <c r="AM12" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AN12" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AO12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AP12">
         <v>0</v>
@@ -3662,17 +3647,17 @@
         <v>44251</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E13" s="2">
         <v>22058</v>
       </c>
       <c r="F13" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>65.775000000000006</v>
+        <v>65.777777777777771</v>
       </c>
       <c r="G13" s="5">
         <v>21.48</v>
@@ -3699,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
@@ -3768,13 +3753,13 @@
         <v>0</v>
       </c>
       <c r="AM13" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AN13" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AO13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AP13">
         <v>0</v>
@@ -3786,7 +3771,7 @@
         <v>54</v>
       </c>
       <c r="AS13" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AV13">
         <v>0</v>
@@ -3795,7 +3780,7 @@
         <v>1</v>
       </c>
       <c r="AX13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AY13">
         <v>1</v>
@@ -3818,17 +3803,17 @@
         <v>44321</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E14" s="2">
         <v>24201</v>
       </c>
       <c r="F14" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>59.908333333333331</v>
+        <v>59.911111111111111</v>
       </c>
       <c r="G14" s="5">
         <v>23.63</v>
@@ -3837,7 +3822,7 @@
         <v>45</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3900,22 +3885,22 @@
         <v>1</v>
       </c>
       <c r="AE14" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG14" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AH14" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AI14" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AJ14" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK14" s="3">
         <v>2</v>
@@ -3924,13 +3909,13 @@
         <v>0</v>
       </c>
       <c r="AM14" s="26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AN14" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AO14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AP14">
         <v>0</v>
@@ -3948,7 +3933,7 @@
         <v>1</v>
       </c>
       <c r="AX14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AY14">
         <v>0</v>
@@ -3971,17 +3956,17 @@
         <v>44335</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E15" s="2">
         <v>30784</v>
       </c>
       <c r="F15" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>41.886111111111113</v>
+        <v>41.888888888888886</v>
       </c>
       <c r="G15" s="5">
         <v>23.65</v>
@@ -4068,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="AJ15" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AK15" s="3">
         <v>2</v>
@@ -4077,13 +4062,13 @@
         <v>1</v>
       </c>
       <c r="AM15" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AN15" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AO15" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AP15">
         <v>0</v>
@@ -4095,10 +4080,10 @@
         <v>50</v>
       </c>
       <c r="AS15" s="28" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AT15" s="28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AV15">
         <v>0</v>
@@ -4107,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="AX15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AY15">
         <v>1</v>
@@ -4130,17 +4115,17 @@
         <v>22</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E16" s="2">
         <v>24041</v>
       </c>
       <c r="F16" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>60.347222222222221</v>
+        <v>60.35</v>
       </c>
       <c r="G16" s="5">
         <v>21.3</v>
@@ -4167,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q16" s="3">
         <v>1</v>
@@ -4233,10 +4218,10 @@
         <v>1</v>
       </c>
       <c r="AM16" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AN16" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AP16">
         <v>0</v>
@@ -4248,10 +4233,10 @@
         <v>50</v>
       </c>
       <c r="AS16" s="28" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AT16" s="28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AV16">
         <v>0</v>
@@ -4260,7 +4245,7 @@
         <v>1</v>
       </c>
       <c r="AX16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AY16">
         <v>0</v>
@@ -4283,17 +4268,17 @@
         <v>44512</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E17" s="2">
         <v>27390</v>
       </c>
       <c r="F17" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>51.177777777777777</v>
+        <v>51.180555555555557</v>
       </c>
       <c r="G17" s="5">
         <v>21.7</v>
@@ -4320,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q17" s="3">
         <v>1</v>
@@ -4392,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="AO17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AP17">
         <v>0</v>
@@ -4410,7 +4395,7 @@
         <v>1</v>
       </c>
       <c r="AX17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AY17">
         <v>1</v>
@@ -4436,14 +4421,14 @@
         <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E18" s="2">
         <v>23082</v>
       </c>
       <c r="F18" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>62.969444444444441</v>
+        <v>62.972222222222221</v>
       </c>
       <c r="G18" s="5">
         <v>25.34</v>
@@ -4461,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4470,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q18" s="3">
         <v>0</v>
@@ -4539,13 +4524,13 @@
         <v>0</v>
       </c>
       <c r="AM18" s="26" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AN18" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AP18">
         <v>0</v>
@@ -4577,23 +4562,23 @@
     </row>
     <row r="19" spans="1:54">
       <c r="A19" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B19" s="2">
         <v>44617</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D19" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E19" s="2">
         <v>23630</v>
       </c>
       <c r="F19" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>61.475000000000001</v>
+        <v>61.477777777777774</v>
       </c>
       <c r="G19" s="5">
         <v>24.41</v>
@@ -4680,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="AJ19" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="AK19" s="3">
         <v>2</v>
@@ -4689,13 +4674,13 @@
         <v>2</v>
       </c>
       <c r="AM19" s="26" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AN19" s="6" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AO19" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AP19">
         <v>0</v>
@@ -4716,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="AX19" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AY19">
         <v>1</v>
@@ -4742,14 +4727,14 @@
         <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E20" s="2">
         <v>21495</v>
       </c>
       <c r="F20" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>67.319444444444443</v>
+        <v>67.322222222222223</v>
       </c>
       <c r="G20" s="5">
         <v>32.81</v>
@@ -4833,25 +4818,25 @@
         <v>1</v>
       </c>
       <c r="AI20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AO20" t="s">
         <v>111</v>
-      </c>
-      <c r="AJ20" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="AO20" t="s">
-        <v>112</v>
       </c>
       <c r="AP20">
         <v>0</v>
@@ -4863,10 +4848,10 @@
         <v>50</v>
       </c>
       <c r="AS20" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AV20" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AW20" s="28">
         <v>0</v>
@@ -4992,7 +4977,7 @@
         <v>18</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>20</v>
@@ -5028,7 +5013,7 @@
         <v>78</v>
       </c>
       <c r="P1" s="24" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="Q1" s="22" t="s">
         <v>6</v>
@@ -5046,7 +5031,7 @@
         <v>3</v>
       </c>
       <c r="V1" s="22" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="W1" s="22" t="s">
         <v>41</v>
@@ -5058,19 +5043,19 @@
         <v>42</v>
       </c>
       <c r="Z1" s="22" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AA1" s="22" t="s">
         <v>24</v>
       </c>
       <c r="AB1" s="22" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AC1" s="22" t="s">
         <v>43</v>
       </c>
       <c r="AD1" s="22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AE1" s="22" t="s">
         <v>11</v>
@@ -5079,7 +5064,7 @@
         <v>60</v>
       </c>
       <c r="AG1" s="22" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AH1" s="22" t="s">
         <v>28</v>
@@ -5175,7 +5160,7 @@
       </c>
       <c r="G2" s="5">
         <f ca="1">YEARFRAC(F2,TODAY())</f>
-        <v>57.866666666666667</v>
+        <v>57.869444444444447</v>
       </c>
       <c r="H2" s="5">
         <v>25.01</v>
@@ -5343,7 +5328,7 @@
       </c>
       <c r="G3" s="5">
         <f t="shared" ref="G3:G30" ca="1" si="0">YEARFRAC(F3,TODAY())</f>
-        <v>77.352777777777774</v>
+        <v>77.355555555555554</v>
       </c>
       <c r="H3" s="5">
         <v>26.44</v>
@@ -5511,7 +5496,7 @@
       </c>
       <c r="G4" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>41.213888888888889</v>
+        <v>41.216666666666669</v>
       </c>
       <c r="H4" s="5">
         <v>21.68</v>
@@ -5607,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="AN4" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AO4" s="7" t="s">
         <v>68</v>
@@ -5666,7 +5651,7 @@
         <v>44244</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>73</v>
@@ -5676,7 +5661,7 @@
       </c>
       <c r="G5" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>54.591666666666669</v>
+        <v>54.594444444444441</v>
       </c>
       <c r="H5" s="5">
         <v>18.21</v>
@@ -5772,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AN5" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AO5" s="6" t="s">
         <v>72</v>
@@ -5796,7 +5781,7 @@
         <v>75</v>
       </c>
       <c r="AV5" s="35" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AW5">
         <v>1</v>
@@ -5837,7 +5822,7 @@
         <v>44026</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>81</v>
@@ -5847,7 +5832,7 @@
       </c>
       <c r="G6" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>46.06111111111111</v>
+        <v>46.06388888888889</v>
       </c>
       <c r="H6" s="5">
         <v>25.55</v>
@@ -5943,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="AN6" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AO6" t="s">
         <v>80</v>
@@ -5999,14 +5984,14 @@
         <v>70</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F7" s="2">
         <v>28651</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>47.725000000000001</v>
+        <v>47.727777777777774</v>
       </c>
       <c r="H7" s="5">
         <v>24.34</v>
@@ -6015,7 +6000,7 @@
         <v>45</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -6093,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL7" s="3">
         <v>2</v>
@@ -6105,10 +6090,10 @@
         <v>0</v>
       </c>
       <c r="AO7" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AP7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AQ7">
         <v>0</v>
@@ -6126,7 +6111,7 @@
         <v>1</v>
       </c>
       <c r="AY7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AZ7">
         <v>1</v>
@@ -6140,8 +6125,8 @@
       <c r="BC7" s="35">
         <v>400</v>
       </c>
-      <c r="BD7" s="35" t="s">
-        <v>84</v>
+      <c r="BD7" s="35">
+        <v>350</v>
       </c>
       <c r="BE7" t="s">
         <v>83</v>
@@ -6161,14 +6146,14 @@
         <v>70</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F8" s="2">
         <v>24762</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>58.37222222222222</v>
+        <v>58.375</v>
       </c>
       <c r="H8" s="5">
         <v>22.1</v>
@@ -6255,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL8" s="3">
         <v>2</v>
@@ -6264,13 +6249,13 @@
         <v>1</v>
       </c>
       <c r="AN8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AO8" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP8" t="s">
         <v>90</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>91</v>
       </c>
       <c r="AQ8">
         <v>0</v>
@@ -6323,14 +6308,14 @@
         <v>70</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F9" s="2">
         <v>24595</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>58.827777777777776</v>
+        <v>58.830555555555556</v>
       </c>
       <c r="H9" s="5">
         <v>23.49</v>
@@ -6426,13 +6411,13 @@
         <v>0</v>
       </c>
       <c r="AN9" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AO9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AP9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AQ9">
         <v>0</v>
@@ -6444,13 +6429,13 @@
         <v>50</v>
       </c>
       <c r="AT9" s="35" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AU9" s="35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AV9" s="35" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AW9">
         <v>0</v>
@@ -6491,14 +6476,14 @@
         <v>70</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F10" s="2">
         <v>24240</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>59.8</v>
+        <v>59.802777777777777</v>
       </c>
       <c r="H10" s="5">
         <v>30.61</v>
@@ -6594,13 +6579,13 @@
         <v>0</v>
       </c>
       <c r="AN10" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AO10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AP10" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="AP10" s="8" t="s">
-        <v>104</v>
       </c>
       <c r="AQ10">
         <v>0</v>
@@ -6650,14 +6635,14 @@
         <v>61</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F11" s="2">
         <v>26926</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>52.45</v>
+        <v>52.452777777777776</v>
       </c>
       <c r="H11" s="5">
         <v>30.72</v>
@@ -6684,7 +6669,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R11" s="3">
         <v>1</v>
@@ -6744,7 +6729,7 @@
         <v>1</v>
       </c>
       <c r="AK11" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL11" s="3">
         <v>0</v>
@@ -6753,13 +6738,13 @@
         <v>0</v>
       </c>
       <c r="AN11" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AO11" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AP11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AQ11">
         <v>0</v>
@@ -6771,10 +6756,10 @@
         <v>50</v>
       </c>
       <c r="AT11" s="35" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AU11" s="35" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AW11">
         <v>0</v>
@@ -6783,7 +6768,7 @@
         <v>1</v>
       </c>
       <c r="AY11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -6818,14 +6803,14 @@
         <v>70</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F12" s="2">
         <v>34325</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>32.19166666666667</v>
+        <v>32.194444444444443</v>
       </c>
       <c r="H12" s="5">
         <v>20.9</v>
@@ -6834,7 +6819,7 @@
         <v>45</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -6855,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="S12" s="3">
         <v>1</v>
@@ -6912,7 +6897,7 @@
         <v>1</v>
       </c>
       <c r="AK12" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL12" s="3">
         <v>2</v>
@@ -6921,13 +6906,13 @@
         <v>1</v>
       </c>
       <c r="AN12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="AO12" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="AP12" t="s">
         <v>172</v>
-      </c>
-      <c r="AO12" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>173</v>
       </c>
       <c r="AQ12">
         <v>0</v>
@@ -6939,13 +6924,13 @@
         <v>50</v>
       </c>
       <c r="AT12" s="35" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AU12" s="35" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AV12" s="35" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AW12">
         <v>0</v>
@@ -6954,7 +6939,7 @@
         <v>1</v>
       </c>
       <c r="AY12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AZ12">
         <v>1</v>
@@ -6968,8 +6953,8 @@
       <c r="BC12" s="35">
         <v>50</v>
       </c>
-      <c r="BD12" s="35" t="s">
-        <v>175</v>
+      <c r="BD12" s="35">
+        <v>282</v>
       </c>
       <c r="BE12" t="s">
         <v>77</v>
@@ -6989,14 +6974,14 @@
         <v>70</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F13" s="2">
         <v>29223</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>46.161111111111111</v>
+        <v>46.163888888888891</v>
       </c>
       <c r="H13" s="5">
         <v>23.96</v>
@@ -7005,7 +6990,7 @@
         <v>45</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -7023,7 +7008,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R13" s="3">
         <v>0</v>
@@ -7092,13 +7077,13 @@
         <v>0</v>
       </c>
       <c r="AN13" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AO13" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AP13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AQ13">
         <v>0</v>
@@ -7127,8 +7112,8 @@
       <c r="BC13" s="35">
         <v>60</v>
       </c>
-      <c r="BD13" s="35" t="s">
-        <v>178</v>
+      <c r="BD13" s="35">
+        <v>350</v>
       </c>
       <c r="BE13" t="s">
         <v>77</v>
@@ -7148,14 +7133,14 @@
         <v>70</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F14" s="2">
         <v>31562</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>39.75277777777778</v>
+        <v>39.755555555555553</v>
       </c>
       <c r="H14" s="5">
         <v>19.309999999999999</v>
@@ -7164,7 +7149,7 @@
         <v>45</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -7239,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL14" s="3">
         <v>2</v>
@@ -7248,13 +7233,13 @@
         <v>0</v>
       </c>
       <c r="AN14" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AO14" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AP14" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AQ14">
         <v>0</v>
@@ -7266,7 +7251,7 @@
         <v>50</v>
       </c>
       <c r="AT14" s="35" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="AW14">
         <v>1</v>
@@ -7275,7 +7260,7 @@
         <v>1</v>
       </c>
       <c r="AY14" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AZ14">
         <v>1</v>
@@ -7310,14 +7295,14 @@
         <v>70</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F15" s="2">
         <v>27291</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>51.45</v>
+        <v>51.452777777777776</v>
       </c>
       <c r="H15" s="5">
         <v>18.54</v>
@@ -7404,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AL15" s="3">
         <v>2</v>
@@ -7413,13 +7398,13 @@
         <v>1</v>
       </c>
       <c r="AN15" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AO15" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AP15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AQ15">
         <v>0</v>
@@ -7431,7 +7416,7 @@
         <v>54</v>
       </c>
       <c r="AT15" s="35" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AW15">
         <v>0</v>
@@ -7472,14 +7457,14 @@
         <v>70</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F16" s="2">
         <v>28651</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>47.725000000000001</v>
+        <v>47.727777777777774</v>
       </c>
       <c r="H16" s="5">
         <v>24.34</v>
@@ -7488,7 +7473,7 @@
         <v>45</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -7566,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL16" s="3">
         <v>2</v>
@@ -7578,10 +7563,10 @@
         <v>0</v>
       </c>
       <c r="AO16" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AP16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AQ16">
         <v>0</v>
@@ -7593,7 +7578,7 @@
         <v>50</v>
       </c>
       <c r="AT16" s="35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AW16">
         <v>0</v>
@@ -7602,7 +7587,7 @@
         <v>1</v>
       </c>
       <c r="AY16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AZ16">
         <v>1</v>
@@ -7616,14 +7601,14 @@
       <c r="BC16" s="35">
         <v>400</v>
       </c>
-      <c r="BD16" s="35" t="s">
-        <v>189</v>
+      <c r="BD16" s="35">
+        <v>350</v>
       </c>
       <c r="BE16" t="s">
         <v>77</v>
       </c>
       <c r="BF16" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:57">
@@ -7640,14 +7625,14 @@
         <v>61</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F17" s="2">
         <v>19534</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>72.686111111111117</v>
+        <v>72.688888888888883</v>
       </c>
       <c r="H17" s="5">
         <v>30.86</v>
@@ -7674,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R17" s="3">
         <v>1</v>
@@ -7734,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AL17" s="3">
         <v>1</v>
@@ -7749,7 +7734,7 @@
         <v>62</v>
       </c>
       <c r="AP17" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="AQ17">
         <v>0</v>
@@ -7799,14 +7784,14 @@
         <v>61</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F18" s="2">
         <v>17617</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>77.933333333333337</v>
+        <v>77.936111111111117</v>
       </c>
       <c r="H18" s="5">
         <v>26.85</v>
@@ -7836,7 +7821,7 @@
         <v>0</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="S18" s="3">
         <v>1</v>
@@ -7902,13 +7887,13 @@
         <v>1</v>
       </c>
       <c r="AN18" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AO18" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="AP18" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="AR18" s="34">
         <v>45071</v>
@@ -7917,13 +7902,13 @@
         <v>50</v>
       </c>
       <c r="AT18" s="35" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AU18" s="35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AV18" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AW18">
         <v>1</v>
@@ -7961,17 +7946,17 @@
         <v>44292</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E19" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F19" s="2">
         <v>28642</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>47.75</v>
+        <v>47.75277777777778</v>
       </c>
       <c r="H19" s="5">
         <v>22.43</v>
@@ -8067,13 +8052,13 @@
         <v>1</v>
       </c>
       <c r="AN19" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AO19" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AP19" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="AQ19">
         <v>0</v>
@@ -8120,17 +8105,17 @@
         <v>44258</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F20" s="2">
         <v>16837</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>80.075000000000003</v>
+        <v>80.077777777777783</v>
       </c>
       <c r="H20" s="5">
         <v>33.020000000000003</v>
@@ -8139,7 +8124,7 @@
         <v>45</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -8160,7 +8145,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R20" s="3">
         <v>1</v>
@@ -8220,7 +8205,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AL20" s="3">
         <v>1</v>
@@ -8232,10 +8217,10 @@
         <v>0</v>
       </c>
       <c r="AO20" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AP20" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AQ20">
         <v>0</v>
@@ -8247,7 +8232,7 @@
         <v>54</v>
       </c>
       <c r="AT20" s="35" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AW20">
         <v>0</v>
@@ -8276,7 +8261,7 @@
     </row>
     <row r="21" spans="1:57">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B21" s="2">
         <v>44113</v>
@@ -8285,17 +8270,17 @@
         <v>44167</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F21" s="2">
         <v>27665</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>50.424999999999997</v>
+        <v>50.427777777777777</v>
       </c>
       <c r="H21" s="5">
         <v>18.989999999999998</v>
@@ -8373,31 +8358,31 @@
         <v>0</v>
       </c>
       <c r="AH21" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AI21" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AJ21" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK21" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AL21" s="3">
         <v>2</v>
       </c>
       <c r="AM21" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AN21" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AO21" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AP21" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AQ21">
         <v>0</v>
@@ -8412,10 +8397,10 @@
         <v>67</v>
       </c>
       <c r="AU21" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AV21" s="35" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AW21">
         <v>0</v>
@@ -8424,7 +8409,7 @@
         <v>1</v>
       </c>
       <c r="AY21" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -8447,7 +8432,7 @@
     </row>
     <row r="22" spans="1:57">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" s="2">
         <v>44148</v>
@@ -8456,17 +8441,17 @@
         <v>44217</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F22" s="2">
         <v>34886</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>30.652777777777779</v>
+        <v>30.655555555555555</v>
       </c>
       <c r="H22" s="5">
         <v>22.5</v>
@@ -8493,7 +8478,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R22" s="3">
         <v>1</v>
@@ -8544,31 +8529,31 @@
         <v>0</v>
       </c>
       <c r="AH22" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AI22" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AJ22" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AK22" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AL22" s="3">
         <v>2</v>
       </c>
       <c r="AM22" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AN22" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AO22" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AP22" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AQ22">
         <v>0</v>
@@ -8618,14 +8603,14 @@
         <v>70</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F23" s="2">
         <v>28867</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>47.136111111111113</v>
+        <v>47.138888888888886</v>
       </c>
       <c r="H23" s="5">
         <v>26</v>
@@ -8652,7 +8637,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R23" s="3">
         <v>1</v>
@@ -8712,7 +8697,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL23" s="3">
         <v>2</v>
@@ -8721,13 +8706,13 @@
         <v>0</v>
       </c>
       <c r="AN23" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AO23" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AP23" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AQ23">
         <v>0</v>
@@ -8739,7 +8724,7 @@
         <v>54</v>
       </c>
       <c r="AT23" s="35" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AW23">
         <v>0</v>
@@ -8777,17 +8762,17 @@
         <v>44344</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F24" s="2">
         <v>23180</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>62.702777777777776</v>
+        <v>62.705555555555556</v>
       </c>
       <c r="H24" s="5">
         <v>28.15</v>
@@ -8874,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AL24" s="3">
         <v>2</v>
@@ -8883,13 +8868,13 @@
         <v>0</v>
       </c>
       <c r="AN24" s="26" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AO24" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AP24" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="AQ24">
         <v>0</v>
@@ -8901,7 +8886,7 @@
         <v>50</v>
       </c>
       <c r="AT24" s="35" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AW24">
         <v>0</v>
@@ -8910,13 +8895,13 @@
         <v>1</v>
       </c>
       <c r="AY24" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AZ24">
         <v>1</v>
       </c>
       <c r="BA24" s="35" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="BB24" s="35">
         <v>750</v>
@@ -8945,14 +8930,14 @@
         <v>70</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F25" s="2">
         <v>15710</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>83.158333333333331</v>
+        <v>83.161111111111111</v>
       </c>
       <c r="H25" s="5">
         <v>22.67</v>
@@ -9039,7 +9024,7 @@
         <v>1</v>
       </c>
       <c r="AK25" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL25" s="3">
         <v>0</v>
@@ -9048,13 +9033,13 @@
         <v>0</v>
       </c>
       <c r="AN25" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AO25" s="6" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AP25" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AR25" s="34">
         <v>45790</v>
@@ -9063,7 +9048,7 @@
         <v>54</v>
       </c>
       <c r="AT25" s="35" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AW25">
         <v>1</v>
@@ -9104,14 +9089,14 @@
         <v>70</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F26" s="2">
         <v>24240</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>59.8</v>
+        <v>59.802777777777777</v>
       </c>
       <c r="H26" s="5">
         <v>30.61</v>
@@ -9210,10 +9195,10 @@
         <v>0</v>
       </c>
       <c r="AO26" s="6" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="AP26" s="6" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AQ26">
         <v>0</v>
@@ -9242,8 +9227,8 @@
       <c r="BB26" s="35">
         <v>550</v>
       </c>
-      <c r="BC26" s="35" t="s">
-        <v>216</v>
+      <c r="BC26" s="35">
+        <v>250</v>
       </c>
       <c r="BD26" s="35">
         <v>400</v>
@@ -9266,14 +9251,14 @@
         <v>70</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F27" s="2">
         <v>27346</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>51.3</v>
+        <v>51.302777777777777</v>
       </c>
       <c r="H27" s="5">
         <v>26.28</v>
@@ -9300,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R27" s="3">
         <v>1</v>
@@ -9360,7 +9345,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL27" s="3">
         <v>2</v>
@@ -9369,13 +9354,13 @@
         <v>1</v>
       </c>
       <c r="AN27" s="26" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AO27" s="6" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AP27" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AQ27">
         <v>0</v>
@@ -9387,10 +9372,10 @@
         <v>54</v>
       </c>
       <c r="AT27" s="35" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AU27" s="35" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="AW27">
         <v>1</v>
@@ -9431,14 +9416,14 @@
         <v>70</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F28" s="2">
         <v>30196</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>43.49722222222222</v>
+        <v>43.5</v>
       </c>
       <c r="H28" s="5">
         <v>27.84</v>
@@ -9465,7 +9450,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R28" s="3">
         <v>1</v>
@@ -9477,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="V28" s="3">
         <v>0</v>
@@ -9534,13 +9519,13 @@
         <v>0</v>
       </c>
       <c r="AN28" s="26" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AO28" s="6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AP28" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AQ28">
         <v>0</v>
@@ -9552,7 +9537,7 @@
         <v>50</v>
       </c>
       <c r="AT28" s="35" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AW28">
         <v>0</v>
@@ -9561,7 +9546,7 @@
         <v>1</v>
       </c>
       <c r="AY28" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AZ28">
         <v>0</v>
@@ -9596,14 +9581,14 @@
         <v>70</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F29" s="2">
         <v>30387</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>42.969444444444441</v>
+        <v>42.972222222222221</v>
       </c>
       <c r="H29" s="5">
         <v>27.25</v>
@@ -9630,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R29" s="3">
         <v>1</v>
@@ -9690,7 +9675,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AL29" s="3">
         <v>2</v>
@@ -9699,13 +9684,13 @@
         <v>0</v>
       </c>
       <c r="AN29" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AO29" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AP29" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AQ29">
         <v>0</v>
@@ -9752,17 +9737,17 @@
         <v>44123</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F30" s="2">
         <v>24627</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>58.741666666666667</v>
+        <v>58.744444444444447</v>
       </c>
       <c r="H30" s="5">
         <v>19.13</v>
@@ -9789,7 +9774,7 @@
         <v>0</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R30" s="3">
         <v>0</v>
@@ -9858,13 +9843,13 @@
         <v>0</v>
       </c>
       <c r="AN30" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AO30" s="6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AP30" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AQ30">
         <v>0</v>
@@ -9876,10 +9861,10 @@
         <v>50</v>
       </c>
       <c r="AT30" s="35" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AU30" s="35" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AV30" s="35" t="s">
         <v>63</v>
@@ -9891,7 +9876,7 @@
         <v>1</v>
       </c>
       <c r="AY30" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AZ30">
         <v>1</v>
